--- a/public/files/copyright-schedule-june-v5.xlsx
+++ b/public/files/copyright-schedule-june-v5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\info\amy\public\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97628E68-0B96-43B5-B729-04D89E59EBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26A39FD1-3E41-4D20-9FD1-6AFA4FC38205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="49890" yWindow="0" windowWidth="16815" windowHeight="20985" tabRatio="500" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="50025" yWindow="0" windowWidth="16980" windowHeight="20985" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI매칭_프롬프트" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="357">
   <si>
     <t>구분</t>
   </si>
@@ -104,9 +104,6 @@
     <t>구찌 (190)</t>
   </si>
   <si>
-    <t>SNS-kering/IG</t>
-  </si>
-  <si>
     <t>매주 2회</t>
   </si>
   <si>
@@ -154,9 +151,6 @@
   </si>
   <si>
     <t>PXG (212)</t>
-  </si>
-  <si>
-    <t>SNS-PXG</t>
   </si>
   <si>
     <t>매주 목요일까지</t>
@@ -1418,10 +1412,6 @@
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
-    <t>SNS-chanel/IG</t>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
     <t>임시계정. 데이터 없으면 담당자 전달</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -1704,54 +1694,6 @@
         <charset val="129"/>
       </rPr>
       <t>/ sk, kt …</t>
-    </r>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>4) (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>신규 매칭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>데이터만 검토 — 기존 매칭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>/실패 데이터</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 제외</t>
     </r>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
@@ -1796,10 +1738,6 @@
       </rPr>
       <t>26.6 스킵</t>
     </r>
-    <phoneticPr fontId="20" type="noConversion"/>
-  </si>
-  <si>
-    <t>※ AI 매칭 기능 활용 시 아래 프롬프트를 (gpt 5.4 mini) 와 함께 사용. (누끼 동일 이미지 매칭)</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
   <si>
@@ -3252,12 +3190,142 @@
 — 확정(이사님) 칸이 채워져야 검토 완료. 빈칸=미검토. 안내 경로: 이사님→팀장님+알바생</t>
     <phoneticPr fontId="20" type="noConversion"/>
   </si>
+  <si>
+    <t>생로랑 (223)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>4) (신규</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매칭) 데이터만</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>검토</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>—</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기존</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>매칭/실패 데이터</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>제외
+(신규 / 실패) 모두 선택된 상태에서는 (실패) 검수된 데이터가 우선 노출되어
+이미 실패로 등록한 데이터를 다시 한번 검수하는 형태가 되므로 매우 중요. (2026-06-22) 퇴근 전 전달 받아 이후부터 적용.</t>
+    </r>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>약 600건/주</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>SNS-PXG (TT/NB/IG)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>SNS-chanel (IG)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
+  <si>
+    <t>SNS-kering (IG)</t>
+    <phoneticPr fontId="20" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38">
+  <fonts count="41">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3518,6 +3586,24 @@
       <color rgb="FFC2334D"/>
       <name val="Noto Sans CJK SC"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -3611,7 +3697,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -3692,11 +3778,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="5" tint="0.59999389629810485"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3723,38 +3818,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3765,7 +3833,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3805,15 +3872,6 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3826,13 +3884,7 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3848,21 +3900,9 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3888,14 +3928,74 @@
     <xf numFmtId="0" fontId="8" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4175,8 +4275,8 @@
   <sheetData>
     <row r="1" spans="1:9" ht="35" customHeight="1">
       <c r="A1" s="6"/>
-      <c r="B1" s="13" t="s">
-        <v>304</v>
+      <c r="B1" s="10" t="s">
+        <v>299</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="6"/>
@@ -4189,7 +4289,7 @@
     <row r="2" spans="1:9">
       <c r="A2" s="6"/>
       <c r="B2" s="9" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -4212,12 +4312,12 @@
     </row>
     <row r="4" spans="1:9" ht="400">
       <c r="B4" s="7" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="9" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -4232,7 +4332,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -4244,990 +4344,1002 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="50" customHeight="1">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="55" t="s">
+        <v>297</v>
+      </c>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+    </row>
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A2" s="56" t="s">
+        <v>298</v>
+      </c>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+    </row>
+    <row r="3" spans="1:9" ht="50" customHeight="1">
+      <c r="A3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="50" customHeight="1">
+      <c r="A4" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="14"/>
+      <c r="H4" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I4" s="14" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="50" customHeight="1">
+      <c r="A5" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="14"/>
+      <c r="H5" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I5" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="50" customHeight="1">
+      <c r="A6" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>351</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I6" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="50" customHeight="1">
+      <c r="A7" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="14"/>
+      <c r="H7" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I7" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="50" customHeight="1">
+      <c r="A8" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>356</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="14"/>
+      <c r="H8" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50" customHeight="1">
+      <c r="A9" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>261</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>355</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I9" s="14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="50" customHeight="1">
+      <c r="A10" s="13" t="s">
+        <v>269</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>353</v>
+      </c>
+      <c r="G10" s="14"/>
+      <c r="H10" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="I10" s="14" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50" customHeight="1">
+      <c r="A11" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" s="14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50" customHeight="1">
+      <c r="A12" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="14" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="100" customHeight="1">
+      <c r="A13" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="14"/>
+      <c r="H13" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="14"/>
+    </row>
+    <row r="14" spans="1:9" ht="100" customHeight="1">
+      <c r="A14" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="14"/>
+      <c r="H14" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="14"/>
+    </row>
+    <row r="15" spans="1:9" ht="100" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="H15" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="14"/>
+    </row>
+    <row r="16" spans="1:9" ht="100" customHeight="1">
+      <c r="A16" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>258</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="G16" s="14"/>
+      <c r="H16" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="I16" s="14"/>
+    </row>
+    <row r="17" spans="1:9" ht="100" customHeight="1">
+      <c r="A17" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="F17" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="G17" s="14"/>
+      <c r="H17" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="100" customHeight="1">
+      <c r="A18" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="F18" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="14" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="100" customHeight="1">
+      <c r="A19" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="F19" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="I19" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="100" customHeight="1">
+      <c r="A20" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="F20" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="100" customHeight="1">
+      <c r="A21" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="C21" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E21" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="F21" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>344</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="100" customHeight="1">
+      <c r="A22" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="14" t="s">
+        <v>257</v>
+      </c>
+      <c r="F22" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="14"/>
+      <c r="H22" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="I22" s="14" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="170" customHeight="1">
+      <c r="A23" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="F23" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="14"/>
+      <c r="H23" s="18" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-    </row>
-    <row r="2" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A2" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
-    </row>
-    <row r="3" spans="1:9" ht="50" customHeight="1">
-      <c r="A3" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>296</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>271</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="21" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="50" customHeight="1">
-      <c r="A4" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="23" t="s">
+      <c r="I23" s="14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="170" customHeight="1">
+      <c r="A24" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E24" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G24" s="14"/>
+      <c r="H24" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="50" customHeight="1">
+      <c r="A25" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="14"/>
+      <c r="H25" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="50" customHeight="1">
+      <c r="A26" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="14"/>
+      <c r="H26" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="50" customHeight="1">
+      <c r="A27" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E27" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G27" s="14"/>
+      <c r="H27" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="I27" s="14" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="180" customHeight="1">
+      <c r="A28" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="F28" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="I28" s="22" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="180" customHeight="1">
+      <c r="A29" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="I29" s="22" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="180" customHeight="1">
+      <c r="A30" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="H30" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="I30" s="22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="100" customHeight="1">
+      <c r="A31" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="H31" s="23" t="s">
+        <v>287</v>
+      </c>
+      <c r="I31" s="14" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="100" customHeight="1">
+      <c r="A32" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="14" t="s">
+        <v>280</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="I32" s="14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="100" customHeight="1">
+      <c r="A33" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="F4" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="23"/>
-      <c r="H4" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="50" customHeight="1">
-      <c r="A5" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="23"/>
-      <c r="H5" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="I5" s="23" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="50" customHeight="1">
-      <c r="A6" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="I6" s="23" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="50" customHeight="1">
-      <c r="A7" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="50" customHeight="1">
-      <c r="A8" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>276</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="I8" s="23" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="50" customHeight="1">
-      <c r="A9" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="I9" s="23" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="50" customHeight="1">
-      <c r="A10" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="22" t="s">
-        <v>274</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="50" customHeight="1">
-      <c r="A11" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>286</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="F11" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="23" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="50" customHeight="1">
-      <c r="A12" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>35</v>
-      </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="25" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" s="23" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="100" customHeight="1">
-      <c r="A13" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B13" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="F13" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="23"/>
-    </row>
-    <row r="14" spans="1:9" ht="100" customHeight="1">
-      <c r="A14" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="I14" s="23"/>
-    </row>
-    <row r="15" spans="1:9" ht="100" customHeight="1">
-      <c r="A15" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="F15" s="23" t="s">
+      <c r="F33" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>98</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>99</v>
+      </c>
+      <c r="I33" s="23"/>
+    </row>
+    <row r="34" spans="1:9" ht="100" customHeight="1">
+      <c r="A34" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="I15" s="23"/>
-    </row>
-    <row r="16" spans="1:9" ht="100" customHeight="1">
-      <c r="A16" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>260</v>
-      </c>
-      <c r="F16" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="G16" s="23"/>
-      <c r="H16" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="I16" s="23"/>
-    </row>
-    <row r="17" spans="1:9" ht="100" customHeight="1">
-      <c r="A17" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F17" s="23" t="s">
-        <v>281</v>
-      </c>
-      <c r="G17" s="23"/>
-      <c r="H17" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="I17" s="23" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="100" customHeight="1">
-      <c r="A18" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="F18" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G18" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="H18" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="I18" s="23" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="100" customHeight="1">
-      <c r="A19" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="F19" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G19" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="H19" s="26" t="s">
-        <v>56</v>
-      </c>
-      <c r="I19" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="100" customHeight="1">
-      <c r="A20" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="F20" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G20" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="H20" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="I20" s="23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="100" customHeight="1">
-      <c r="A21" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>287</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="F21" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>349</v>
-      </c>
-      <c r="H21" s="26" t="s">
-        <v>60</v>
-      </c>
-      <c r="I21" s="23" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="100" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E22" s="23" t="s">
-        <v>259</v>
-      </c>
-      <c r="F22" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="23"/>
-      <c r="H22" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="I22" s="23" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="170" customHeight="1">
-      <c r="A23" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F23" s="23" t="s">
-        <v>68</v>
-      </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="I23" s="23" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="170" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E24" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F24" s="23" t="s">
-        <v>70</v>
-      </c>
-      <c r="G24" s="23"/>
-      <c r="H24" s="28" t="s">
-        <v>307</v>
-      </c>
-      <c r="I24" s="23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="50" customHeight="1">
-      <c r="A25" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="23" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="50" customHeight="1">
-      <c r="A26" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F26" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="23"/>
-      <c r="H26" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="I26" s="23" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="50" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>280</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="I27" s="23" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="180" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="F28" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="H28" s="29" t="s">
-        <v>314</v>
-      </c>
-      <c r="I28" s="32" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="180" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B29" s="30" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="F29" s="29" t="s">
-        <v>41</v>
-      </c>
-      <c r="G29" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="I29" s="32" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="180" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="D30" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="F30" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="H30" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="I30" s="32" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="100" customHeight="1">
-      <c r="A31" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>79</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>306</v>
-      </c>
-      <c r="H31" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="I31" s="23" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="100" customHeight="1">
-      <c r="A32" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>290</v>
-      </c>
-      <c r="H32" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="I32" s="23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="100" customHeight="1">
-      <c r="A33" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B33" s="33" t="s">
+      <c r="F34" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="C33" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="D33" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="E33" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="F33" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="G33" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="H33" s="33" t="s">
+      <c r="G34" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="I33" s="33"/>
-    </row>
-    <row r="34" spans="1:9" ht="100" customHeight="1">
-      <c r="A34" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="B34" s="33" t="s">
+      <c r="H34" s="23" t="s">
         <v>102</v>
       </c>
-      <c r="C34" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="D34" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="E34" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="F34" s="33" t="s">
-        <v>99</v>
-      </c>
-      <c r="G34" s="33" t="s">
+      <c r="I34" s="23" t="s">
         <v>103</v>
-      </c>
-      <c r="H34" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="I34" s="33" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="19.5" customHeight="1"/>
     <row r="36" spans="1:9" ht="35" customHeight="1">
-      <c r="A36" s="14" t="s">
-        <v>305</v>
-      </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="15"/>
+      <c r="A36" s="58" t="s">
+        <v>300</v>
+      </c>
+      <c r="B36" s="59"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
     </row>
     <row r="37" spans="1:9" ht="30" customHeight="1">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+    </row>
+    <row r="38" spans="1:9" ht="30" customHeight="1">
+      <c r="A38" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+    </row>
+    <row r="39" spans="1:9" ht="50" customHeight="1">
+      <c r="A39" s="54" t="s">
+        <v>285</v>
+      </c>
+      <c r="B39" s="54"/>
+      <c r="C39" s="54"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="54"/>
+      <c r="F39" s="54"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="54"/>
+      <c r="I39" s="54"/>
+    </row>
+    <row r="40" spans="1:9" ht="30" customHeight="1">
+      <c r="A40" s="57" t="s">
         <v>106</v>
       </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="16"/>
-      <c r="G37" s="16"/>
-      <c r="H37" s="16"/>
-      <c r="I37" s="16"/>
-    </row>
-    <row r="38" spans="1:9" ht="30" customHeight="1">
-      <c r="A38" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16"/>
-    </row>
-    <row r="39" spans="1:9" ht="50" customHeight="1">
-      <c r="A39" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-    </row>
-    <row r="40" spans="1:9" ht="30" customHeight="1">
-      <c r="A40" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
-      <c r="H40" s="16"/>
-      <c r="I40" s="16"/>
-    </row>
-    <row r="41" spans="1:9" ht="30" customHeight="1">
-      <c r="A41" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
-      <c r="G41" s="18"/>
-      <c r="H41" s="18"/>
-      <c r="I41" s="18"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+    </row>
+    <row r="41" spans="1:9" ht="75" customHeight="1">
+      <c r="A41" s="53" t="s">
+        <v>352</v>
+      </c>
+      <c r="B41" s="53"/>
+      <c r="C41" s="53"/>
+      <c r="D41" s="53"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="53"/>
+      <c r="H41" s="53"/>
+      <c r="I41" s="53"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="51"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A42:I42"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A39:I39"/>
     <mergeCell ref="A1:I1"/>
@@ -5256,216 +5368,216 @@
     <col min="3" max="3" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" s="68" customFormat="1" ht="35" customHeight="1">
-      <c r="B1" s="54" t="s">
-        <v>350</v>
-      </c>
-      <c r="C1" s="54"/>
+    <row r="1" spans="2:3" s="48" customFormat="1" ht="35" customHeight="1">
+      <c r="B1" s="49" t="s">
+        <v>345</v>
+      </c>
+      <c r="C1" s="49"/>
     </row>
     <row r="2" spans="2:3" ht="50" customHeight="1">
-      <c r="B2" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="C2" s="38"/>
+      <c r="B2" s="50" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2" s="50"/>
     </row>
     <row r="4" spans="2:3" ht="15" customHeight="1">
-      <c r="B4" s="34" t="s">
+      <c r="B4" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="15" customHeight="1">
+      <c r="B5" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="C5" s="26" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="15" customHeight="1">
-      <c r="B5" s="35" t="s">
+    <row r="6" spans="2:3" ht="15" customHeight="1">
+      <c r="B6" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="36" t="s">
+      <c r="C6" s="26" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="2:3" ht="15" customHeight="1">
-      <c r="B6" s="35" t="s">
+    <row r="7" spans="2:3" ht="15" customHeight="1">
+      <c r="B7" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="36" t="s">
+      <c r="C7" s="26" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="15" customHeight="1">
-      <c r="B7" s="35" t="s">
+    <row r="8" spans="2:3" ht="15" customHeight="1">
+      <c r="B8" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C8" s="26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" ht="15" customHeight="1">
+      <c r="B9" s="25" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" ht="15" customHeight="1">
-      <c r="B8" s="35" t="s">
+      <c r="C9" s="26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" ht="15" customHeight="1">
+      <c r="B10" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="C8" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="35" t="s">
+      <c r="C10" s="26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" ht="15" customHeight="1">
+      <c r="B11" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" ht="15" customHeight="1">
-      <c r="B10" s="35" t="s">
+      <c r="C11" s="26" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="36" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="11" spans="2:3" ht="15" customHeight="1">
-      <c r="B11" s="35" t="s">
+    </row>
+    <row r="12" spans="2:3" ht="15" customHeight="1">
+      <c r="B12" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="C11" s="36" t="s">
+      <c r="C12" s="26" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="2:3" ht="15" customHeight="1">
-      <c r="B12" s="35" t="s">
+    <row r="13" spans="2:3" ht="15" customHeight="1">
+      <c r="B13" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="C13" s="26" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="15" customHeight="1">
-      <c r="B13" s="35" t="s">
+    <row r="14" spans="2:3" ht="15" customHeight="1">
+      <c r="B14" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="36" t="s">
+      <c r="C14" s="26" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="14" spans="2:3" ht="15" customHeight="1">
-      <c r="B14" s="35" t="s">
+    <row r="15" spans="2:3" ht="15" customHeight="1">
+      <c r="B15" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="C14" s="36" t="s">
+      <c r="C15" s="26" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="15" customHeight="1">
-      <c r="B15" s="35" t="s">
+    <row r="16" spans="2:3" ht="15" customHeight="1">
+      <c r="B16" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C16" s="26" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="35" t="s">
+    <row r="17" spans="2:3" ht="15" customHeight="1">
+      <c r="B17" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="36" t="s">
+      <c r="C17" s="26" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="35" t="s">
+    <row r="18" spans="2:3" ht="15" customHeight="1">
+      <c r="B18" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C18" s="26" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="15" customHeight="1">
-      <c r="B18" s="35" t="s">
+    <row r="19" spans="2:3" ht="15" customHeight="1">
+      <c r="B19" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="36" t="s">
+      <c r="C19" s="26" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="15" customHeight="1">
-      <c r="B19" s="35" t="s">
+    <row r="20" spans="2:3" ht="15" customHeight="1">
+      <c r="B20" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="36" t="s">
+      <c r="C20" s="26" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="15" customHeight="1">
+      <c r="B21" s="25" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="20" spans="2:3" ht="15" customHeight="1">
-      <c r="B20" s="35" t="s">
+      <c r="C21" s="26" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="15" customHeight="1">
+      <c r="B22" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="C20" s="36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="B21" s="35" t="s">
+      <c r="C22" s="26" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="15" customHeight="1">
+      <c r="B23" s="25" t="s">
         <v>139</v>
       </c>
-      <c r="C21" s="36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" ht="15" customHeight="1">
-      <c r="B22" s="35" t="s">
+      <c r="C23" s="26" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="15" customHeight="1">
+      <c r="B24" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="C22" s="36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" ht="15" customHeight="1">
-      <c r="B23" s="35" t="s">
+      <c r="C24" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="C23" s="36" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="15" customHeight="1">
-      <c r="B24" s="37" t="s">
+    </row>
+    <row r="25" spans="2:3" ht="15" customHeight="1">
+      <c r="B25" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="36" t="s">
+      <c r="C25" s="26" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" ht="15" customHeight="1">
+      <c r="B26" s="25" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="25" spans="2:3" ht="15" customHeight="1">
-      <c r="B25" s="35" t="s">
+      <c r="C26" s="26" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="15" customHeight="1">
+      <c r="B27" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="C25" s="36" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="26" spans="2:3" ht="15" customHeight="1">
-      <c r="B26" s="35" t="s">
+      <c r="C27" s="26" t="s">
         <v>145</v>
       </c>
-      <c r="C26" s="36" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" ht="15" customHeight="1">
-      <c r="B27" s="35" t="s">
+    </row>
+    <row r="28" spans="2:3" ht="15" customHeight="1">
+      <c r="B28" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="C27" s="36" t="s">
+      <c r="C28" s="26" t="s">
         <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="2:3" ht="15" customHeight="1">
-      <c r="B28" s="37" t="s">
-        <v>148</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -5494,26 +5606,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
+      <c r="A1" s="60" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
     </row>
     <row r="2" spans="1:5" ht="27.75" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
@@ -5521,121 +5633,121 @@
     </row>
     <row r="3" spans="1:5" ht="16.5" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="D3" s="65" t="s">
-        <v>153</v>
+        <v>337</v>
+      </c>
+      <c r="D3" s="46" t="s">
+        <v>151</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="D4" s="65" t="s">
-        <v>153</v>
+        <v>338</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>151</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>153</v>
+        <v>338</v>
+      </c>
+      <c r="D5" s="46" t="s">
+        <v>151</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="D6" s="65" t="s">
-        <v>153</v>
+        <v>338</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>151</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="D7" s="65" t="s">
+        <v>338</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="D8" s="66" t="s">
-        <v>156</v>
+        <v>328</v>
+      </c>
+      <c r="D8" s="47" t="s">
+        <v>154</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="D9" s="65" t="s">
-        <v>153</v>
+        <v>340</v>
+      </c>
+      <c r="D9" s="46" t="s">
+        <v>151</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -5663,25 +5775,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
-      <c r="A1" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
+      <c r="A1" s="60" t="s">
+        <v>346</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
     </row>
     <row r="2" spans="1:4" ht="27.75" customHeight="1">
       <c r="A2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="35" customHeight="1">
@@ -5689,13 +5801,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="35" customHeight="1">
@@ -5703,13 +5815,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1">
@@ -5717,13 +5829,13 @@
         <v>3</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>168</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="20" customHeight="1">
@@ -5731,13 +5843,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="20" customHeight="1">
@@ -5745,13 +5857,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="20" customHeight="1">
@@ -5759,13 +5871,13 @@
         <v>6</v>
       </c>
       <c r="B8" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>174</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="20" customHeight="1">
@@ -5773,13 +5885,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="20" customHeight="1">
@@ -5787,13 +5899,13 @@
         <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="150" customHeight="1">
@@ -5801,11 +5913,11 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
   </sheetData>
@@ -5833,12 +5945,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
-      <c r="A1" s="69" t="s">
-        <v>352</v>
-      </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
+      <c r="A1" s="62" t="s">
+        <v>347</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
     </row>
     <row r="2" spans="1:4" ht="27.75" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -5851,441 +5963,441 @@
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="16.5" customHeight="1">
       <c r="A3" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5" customHeight="1">
       <c r="A4" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="16.5" customHeight="1">
       <c r="A5" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="16.5" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="16.5" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.5" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="16.5" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="16.5" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>94</v>
-      </c>
     </row>
     <row r="14" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A14" s="63" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="64" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="64" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="63" t="s">
-        <v>159</v>
+      <c r="A14" s="44" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A15" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="36" t="s">
+      <c r="A15" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D15" s="26" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A16" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A17" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A18" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A19" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A20" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="C20" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A21" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A22" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A23" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A24" s="26" t="s">
+        <v>277</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A25" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A26" s="26" t="s">
+        <v>273</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A27" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D27" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A28" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D28" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A29" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A30" s="26" t="s">
+        <v>270</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="16.5" customHeight="1">
+      <c r="A31" s="26" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A16" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B16" s="36" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="36" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A17" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B17" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="36" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A18" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A19" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B19" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="36" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A20" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A21" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B21" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A22" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B22" s="36" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A23" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="36" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A24" s="36" t="s">
-        <v>280</v>
-      </c>
-      <c r="B24" s="36" t="s">
+      <c r="B31" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="36" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A25" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="B25" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="D25" s="36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A26" s="36" t="s">
-        <v>276</v>
-      </c>
-      <c r="B26" s="36" t="s">
+      <c r="D31" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D26" s="36" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A27" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="B27" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="D27" s="36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A28" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="B28" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C28" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="D28" s="36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A29" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="B29" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="D29" s="36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A30" s="36" t="s">
-        <v>273</v>
-      </c>
-      <c r="B30" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="D30" s="36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A31" s="36" t="s">
-        <v>284</v>
-      </c>
-      <c r="B31" s="36" t="s">
-        <v>102</v>
-      </c>
-      <c r="C31" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="D31" s="36" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="32" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A32" s="36" t="s">
-        <v>278</v>
-      </c>
-      <c r="B32" s="36" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" s="36" t="s">
-        <v>333</v>
+      <c r="A32" s="26" t="s">
+        <v>275</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="C32" s="26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D32" s="26" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="16.5" customHeight="1">
-      <c r="A33" s="36" t="s">
-        <v>186</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="D33" s="36" t="s">
-        <v>26</v>
+      <c r="A33" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D33" s="26" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -6312,173 +6424,173 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" ht="24" customHeight="1">
-      <c r="B1" s="70" t="s">
-        <v>353</v>
-      </c>
-      <c r="C1" s="70"/>
+      <c r="B1" s="63" t="s">
+        <v>348</v>
+      </c>
+      <c r="C1" s="63"/>
     </row>
     <row r="2" spans="2:3" ht="30" customHeight="1">
-      <c r="B2" s="55" t="s">
-        <v>298</v>
-      </c>
-      <c r="C2" s="55"/>
+      <c r="B2" s="64" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" s="64"/>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
     </row>
     <row r="4" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B5" s="39" t="s">
+        <v>325</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B6" s="39" t="s">
+        <v>327</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="C4" s="36" t="s">
+    </row>
+    <row r="7" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B7" s="39" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B5" s="57" t="s">
-        <v>330</v>
-      </c>
-      <c r="C5" s="36" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B6" s="57" t="s">
-        <v>332</v>
-      </c>
-      <c r="C6" s="36" t="s">
+      <c r="C7" s="26" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B7" s="57" t="s">
+    <row r="8" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B8" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="C8" s="26" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="8" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B8" s="57" t="s">
+    <row r="9" spans="2:3" ht="19.5" customHeight="1">
+      <c r="B9" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C9" s="26" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="19.5" customHeight="1">
-      <c r="B9" s="57" t="s">
+    <row r="11" spans="2:3" ht="24" customHeight="1">
+      <c r="B11" s="63" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="63"/>
+    </row>
+    <row r="12" spans="2:3" ht="300" customHeight="1">
+      <c r="B12" s="65" t="s">
         <v>194</v>
       </c>
-      <c r="C9" s="36" t="s">
+      <c r="C12" s="65"/>
+    </row>
+    <row r="14" spans="2:3" ht="24" customHeight="1">
+      <c r="B14" s="63" t="s">
+        <v>349</v>
+      </c>
+      <c r="C14" s="63"/>
+    </row>
+    <row r="15" spans="2:3" ht="15" customHeight="1">
+      <c r="B15" s="40" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" ht="24" customHeight="1">
-      <c r="B11" s="70" t="s">
-        <v>329</v>
-      </c>
-      <c r="C11" s="70"/>
-    </row>
-    <row r="12" spans="2:3" ht="300" customHeight="1">
-      <c r="B12" s="58" t="s">
+      <c r="C15" s="41" t="s">
         <v>196</v>
       </c>
-      <c r="C12" s="58"/>
-    </row>
-    <row r="14" spans="2:3" ht="24" customHeight="1">
-      <c r="B14" s="70" t="s">
-        <v>354</v>
-      </c>
-      <c r="C14" s="70"/>
-    </row>
-    <row r="15" spans="2:3" ht="15" customHeight="1">
-      <c r="B15" s="59" t="s">
+    </row>
+    <row r="16" spans="2:3" ht="15" customHeight="1">
+      <c r="B16" s="42" t="s">
         <v>197</v>
       </c>
-      <c r="C15" s="60" t="s">
+      <c r="C16" s="43" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="61" t="s">
+    <row r="17" spans="2:3" ht="15" customHeight="1">
+      <c r="B17" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C17" s="41" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="59" t="s">
+    <row r="18" spans="2:3" ht="15" customHeight="1">
+      <c r="B18" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="C17" s="60" t="s">
+      <c r="C18" s="43" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="18" spans="2:3" ht="15" customHeight="1">
-      <c r="B18" s="61" t="s">
+    <row r="19" spans="2:3" ht="15" customHeight="1">
+      <c r="B19" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="C18" s="62" t="s">
+      <c r="C19" s="41" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="19" spans="2:3" ht="15" customHeight="1">
-      <c r="B19" s="59" t="s">
+    <row r="20" spans="2:3" ht="15" customHeight="1">
+      <c r="B20" s="42" t="s">
         <v>205</v>
       </c>
-      <c r="C19" s="60" t="s">
+      <c r="C20" s="43" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="20" spans="2:3" ht="15" customHeight="1">
-      <c r="B20" s="61" t="s">
+    <row r="21" spans="2:3" ht="15" customHeight="1">
+      <c r="B21" s="40" t="s">
         <v>207</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C21" s="41" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="B21" s="59" t="s">
+    <row r="22" spans="2:3" ht="15" customHeight="1">
+      <c r="B22" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="C21" s="60" t="s">
+      <c r="C22" s="43" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="22" spans="2:3" ht="15" customHeight="1">
-      <c r="B22" s="61" t="s">
+    <row r="23" spans="2:3" ht="15" customHeight="1">
+      <c r="B23" s="40" t="s">
         <v>211</v>
       </c>
-      <c r="C22" s="62" t="s">
+      <c r="C23" s="41" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="23" spans="2:3" ht="15" customHeight="1">
-      <c r="B23" s="59" t="s">
+    <row r="24" spans="2:3" ht="15" customHeight="1">
+      <c r="B24" s="42" t="s">
         <v>213</v>
       </c>
-      <c r="C23" s="60" t="s">
+      <c r="C24" s="43" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="24" spans="2:3" ht="15" customHeight="1">
-      <c r="B24" s="61" t="s">
+    <row r="25" spans="2:3" ht="15" customHeight="1">
+      <c r="B25" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C25" s="41" t="s">
         <v>216</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" ht="15" customHeight="1">
-      <c r="B25" s="59" t="s">
-        <v>217</v>
-      </c>
-      <c r="C25" s="60" t="s">
-        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -6509,92 +6621,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="35" customHeight="1">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="66" t="s">
+        <v>217</v>
+      </c>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+    </row>
+    <row r="2" spans="2:4" ht="42" customHeight="1">
+      <c r="B2" s="67" t="s">
+        <v>294</v>
+      </c>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+    </row>
+    <row r="3" spans="2:4" ht="21.5" customHeight="1">
+      <c r="B3" s="68" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+    </row>
+    <row r="4" spans="2:4" ht="35" customHeight="1">
+      <c r="B4" s="28" t="s">
         <v>219</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-    </row>
-    <row r="2" spans="2:4" ht="42" customHeight="1">
-      <c r="B2" s="39" t="s">
-        <v>299</v>
-      </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-    </row>
-    <row r="3" spans="2:4" ht="21.5" customHeight="1">
-      <c r="B3" s="40" t="s">
+      <c r="C4" s="28" t="s">
         <v>220</v>
       </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-    </row>
-    <row r="4" spans="2:4" ht="35" customHeight="1">
-      <c r="B4" s="41" t="s">
+      <c r="D4" s="28" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="41" t="s">
+    </row>
+    <row r="5" spans="2:4" ht="55.5" customHeight="1">
+      <c r="B5" s="29" t="s">
         <v>222</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="C5" s="30" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" ht="55.5" customHeight="1">
-      <c r="B5" s="42" t="s">
+      <c r="D5" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="C5" s="43" t="s">
+    </row>
+    <row r="6" spans="2:4" ht="55.5" customHeight="1">
+      <c r="B6" s="31" t="s">
         <v>225</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="C6" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="D6" s="11" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="55.5" customHeight="1">
-      <c r="B6" s="44" t="s">
+    <row r="7" spans="2:4" ht="55.5" customHeight="1">
+      <c r="B7" s="29" t="s">
         <v>227</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>317</v>
-      </c>
-      <c r="D6" s="45" t="s">
+      <c r="C7" s="30" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" ht="55.5" customHeight="1">
-      <c r="B7" s="42" t="s">
+      <c r="D7" s="30" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="55.5" customHeight="1">
+      <c r="B8" s="31" t="s">
         <v>229</v>
       </c>
-      <c r="C7" s="43" t="s">
+      <c r="C8" s="11" t="s">
         <v>230</v>
       </c>
-      <c r="D7" s="43" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="55.5" customHeight="1">
-      <c r="B8" s="44" t="s">
+      <c r="D8" s="11" t="s">
         <v>231</v>
       </c>
-      <c r="C8" s="45" t="s">
-        <v>232</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>233</v>
-      </c>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="46"/>
-      <c r="C9" s="46"/>
-      <c r="D9" s="46"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
     </row>
     <row r="10" spans="2:4" ht="42" customHeight="1">
-      <c r="B10" s="39" t="s">
-        <v>316</v>
-      </c>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
+      <c r="B10" s="67" t="s">
+        <v>311</v>
+      </c>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -6626,587 +6738,587 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="35" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="70" t="s">
+        <v>232</v>
+      </c>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+    </row>
+    <row r="2" spans="1:7" ht="42" customHeight="1">
+      <c r="A2" s="71" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="71"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+    </row>
+    <row r="3" spans="1:7" ht="30" customHeight="1">
+      <c r="A3" s="33" t="s">
+        <v>219</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="C3" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="E3" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="F3" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="G3" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-    </row>
-    <row r="2" spans="1:7" ht="42" customHeight="1">
-      <c r="A2" s="47" t="s">
-        <v>355</v>
-      </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-    </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1">
-      <c r="A3" s="48" t="s">
-        <v>221</v>
-      </c>
-      <c r="B3" s="48" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A4" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="34"/>
+      <c r="E4" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F4" s="35"/>
+      <c r="G4" s="34"/>
+    </row>
+    <row r="5" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A5" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F5" s="37"/>
+      <c r="G5" s="36"/>
+    </row>
+    <row r="6" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A6" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F6" s="35"/>
+      <c r="G6" s="34"/>
+    </row>
+    <row r="7" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A7" s="36" t="s">
+        <v>201</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F7" s="37"/>
+      <c r="G7" s="36"/>
+    </row>
+    <row r="8" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A8" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F8" s="35"/>
+      <c r="G8" s="34"/>
+    </row>
+    <row r="9" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A9" s="36" t="s">
+        <v>205</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F9" s="37"/>
+      <c r="G9" s="36"/>
+    </row>
+    <row r="10" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A10" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="B10" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="34"/>
+      <c r="E10" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F10" s="35"/>
+      <c r="G10" s="34"/>
+    </row>
+    <row r="11" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A11" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F11" s="37"/>
+      <c r="G11" s="36"/>
+    </row>
+    <row r="12" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A12" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="B12" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C12" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="D12" s="34"/>
+      <c r="E12" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="35"/>
+      <c r="G12" s="34"/>
+    </row>
+    <row r="13" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A13" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F13" s="37"/>
+      <c r="G13" s="36"/>
+    </row>
+    <row r="14" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A14" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F14" s="35"/>
+      <c r="G14" s="34"/>
+    </row>
+    <row r="15" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A15" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" s="37"/>
+      <c r="G15" s="36"/>
+    </row>
+    <row r="16" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A16" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="B16" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F16" s="35"/>
+      <c r="G16" s="34"/>
+    </row>
+    <row r="17" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A17" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F17" s="37"/>
+      <c r="G17" s="36"/>
+    </row>
+    <row r="18" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A18" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="B18" s="35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F18" s="35"/>
+      <c r="G18" s="34"/>
+    </row>
+    <row r="19" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A19" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F19" s="37"/>
+      <c r="G19" s="36"/>
+    </row>
+    <row r="20" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A20" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="B20" s="35" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F20" s="35"/>
+      <c r="G20" s="34"/>
+    </row>
+    <row r="21" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A21" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="B21" s="37" t="s">
         <v>320</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="C21" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F21" s="37"/>
+      <c r="G21" s="36"/>
+    </row>
+    <row r="22" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A22" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="B22" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F22" s="35"/>
+      <c r="G22" s="34"/>
+    </row>
+    <row r="23" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A23" s="36" t="s">
+        <v>244</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="36"/>
+      <c r="E23" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F23" s="37"/>
+      <c r="G23" s="36"/>
+    </row>
+    <row r="24" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A24" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F24" s="35"/>
+      <c r="G24" s="34"/>
+    </row>
+    <row r="25" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A25" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F25" s="37"/>
+      <c r="G25" s="36"/>
+    </row>
+    <row r="26" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A26" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="34"/>
+      <c r="E26" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F26" s="35"/>
+      <c r="G26" s="34"/>
+    </row>
+    <row r="27" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A27" s="36" t="s">
+        <v>248</v>
+      </c>
+      <c r="B27" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="36"/>
+      <c r="E27" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F27" s="37"/>
+      <c r="G27" s="36"/>
+    </row>
+    <row r="28" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A28" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" s="35"/>
+      <c r="G28" s="34"/>
+    </row>
+    <row r="29" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A29" s="36" t="s">
+        <v>250</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F29" s="37"/>
+      <c r="G29" s="36"/>
+    </row>
+    <row r="30" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A30" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="34"/>
+      <c r="E30" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F30" s="35"/>
+      <c r="G30" s="34"/>
+    </row>
+    <row r="31" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A31" s="36" t="s">
+        <v>252</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>182</v>
+      </c>
+      <c r="C31" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="E3" s="48" t="s">
-        <v>322</v>
-      </c>
-      <c r="F3" s="48" t="s">
+      <c r="D31" s="36"/>
+      <c r="E31" s="36" t="s">
         <v>235</v>
       </c>
-      <c r="G3" s="48" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A4" s="49" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="49"/>
-      <c r="E4" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F4" s="50"/>
-      <c r="G4" s="49"/>
-    </row>
-    <row r="5" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A5" s="51" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="52" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F5" s="52"/>
-      <c r="G5" s="51"/>
-    </row>
-    <row r="6" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A6" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="B6" s="50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F6" s="50"/>
-      <c r="G6" s="49"/>
-    </row>
-    <row r="7" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A7" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="B7" s="52" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="52" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F7" s="52"/>
-      <c r="G7" s="51"/>
-    </row>
-    <row r="8" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A8" s="49" t="s">
-        <v>205</v>
-      </c>
-      <c r="B8" s="50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="50" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="49"/>
-    </row>
-    <row r="9" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A9" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="52" t="s">
+      <c r="F31" s="37"/>
+      <c r="G31" s="36"/>
+    </row>
+    <row r="32" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A32" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F32" s="35"/>
+      <c r="G32" s="34"/>
+    </row>
+    <row r="33" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A33" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="B33" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" s="37" t="s">
+        <v>97</v>
+      </c>
+      <c r="D33" s="36"/>
+      <c r="E33" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="F33" s="37"/>
+      <c r="G33" s="36"/>
+    </row>
+    <row r="34" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A34" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="B34" s="35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="F34" s="35"/>
+      <c r="G34" s="34"/>
+    </row>
+    <row r="36" spans="1:7" ht="43.5" customHeight="1">
+      <c r="A36" s="69" t="s">
         <v>323</v>
       </c>
-      <c r="C9" s="52" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F9" s="52"/>
-      <c r="G9" s="51"/>
-    </row>
-    <row r="10" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A10" s="49" t="s">
-        <v>209</v>
-      </c>
-      <c r="B10" s="50" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="50" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="49"/>
-      <c r="E10" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="49"/>
-    </row>
-    <row r="11" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A11" s="51" t="s">
-        <v>211</v>
-      </c>
-      <c r="B11" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="52" t="s">
-        <v>31</v>
-      </c>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F11" s="52"/>
-      <c r="G11" s="51"/>
-    </row>
-    <row r="12" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A12" s="49" t="s">
-        <v>213</v>
-      </c>
-      <c r="B12" s="50" t="s">
-        <v>324</v>
-      </c>
-      <c r="C12" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="49"/>
-    </row>
-    <row r="13" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A13" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="B13" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="C13" s="52" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="51"/>
-      <c r="E13" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F13" s="52"/>
-      <c r="G13" s="51"/>
-    </row>
-    <row r="14" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A14" s="49" t="s">
-        <v>217</v>
-      </c>
-      <c r="B14" s="50" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F14" s="50"/>
-      <c r="G14" s="49"/>
-    </row>
-    <row r="15" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A15" s="51" t="s">
-        <v>238</v>
-      </c>
-      <c r="B15" s="52" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="51"/>
-      <c r="E15" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F15" s="52"/>
-      <c r="G15" s="51"/>
-    </row>
-    <row r="16" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A16" s="49" t="s">
-        <v>239</v>
-      </c>
-      <c r="B16" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="49"/>
-    </row>
-    <row r="17" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A17" s="51" t="s">
-        <v>240</v>
-      </c>
-      <c r="B17" s="52" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F17" s="52"/>
-      <c r="G17" s="51"/>
-    </row>
-    <row r="18" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A18" s="49" t="s">
-        <v>241</v>
-      </c>
-      <c r="B18" s="50" t="s">
-        <v>50</v>
-      </c>
-      <c r="C18" s="50" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F18" s="50"/>
-      <c r="G18" s="49"/>
-    </row>
-    <row r="19" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A19" s="51" t="s">
-        <v>242</v>
-      </c>
-      <c r="B19" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F19" s="52"/>
-      <c r="G19" s="51"/>
-    </row>
-    <row r="20" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A20" s="49" t="s">
-        <v>243</v>
-      </c>
-      <c r="B20" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="C20" s="50" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F20" s="50"/>
-      <c r="G20" s="49"/>
-    </row>
-    <row r="21" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A21" s="51" t="s">
-        <v>244</v>
-      </c>
-      <c r="B21" s="52" t="s">
-        <v>325</v>
-      </c>
-      <c r="C21" s="52" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="51"/>
-      <c r="E21" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F21" s="52"/>
-      <c r="G21" s="51"/>
-    </row>
-    <row r="22" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A22" s="49" t="s">
-        <v>245</v>
-      </c>
-      <c r="B22" s="50" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="D22" s="49"/>
-      <c r="E22" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F22" s="50"/>
-      <c r="G22" s="49"/>
-    </row>
-    <row r="23" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A23" s="51" t="s">
-        <v>246</v>
-      </c>
-      <c r="B23" s="52" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="52" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F23" s="52"/>
-      <c r="G23" s="51"/>
-    </row>
-    <row r="24" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A24" s="49" t="s">
-        <v>247</v>
-      </c>
-      <c r="B24" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="49"/>
-      <c r="E24" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F24" s="50"/>
-      <c r="G24" s="49"/>
-    </row>
-    <row r="25" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A25" s="51" t="s">
-        <v>248</v>
-      </c>
-      <c r="B25" s="52" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="52" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="51"/>
-      <c r="E25" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F25" s="52"/>
-      <c r="G25" s="51"/>
-    </row>
-    <row r="26" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A26" s="49" t="s">
-        <v>249</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" s="49"/>
-      <c r="E26" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F26" s="50"/>
-      <c r="G26" s="49"/>
-    </row>
-    <row r="27" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A27" s="51" t="s">
-        <v>250</v>
-      </c>
-      <c r="B27" s="52" t="s">
-        <v>77</v>
-      </c>
-      <c r="C27" s="52" t="s">
-        <v>76</v>
-      </c>
-      <c r="D27" s="51"/>
-      <c r="E27" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F27" s="52"/>
-      <c r="G27" s="51"/>
-    </row>
-    <row r="28" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A28" s="49" t="s">
-        <v>251</v>
-      </c>
-      <c r="B28" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="D28" s="49"/>
-      <c r="E28" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F28" s="50"/>
-      <c r="G28" s="49"/>
-    </row>
-    <row r="29" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A29" s="51" t="s">
-        <v>252</v>
-      </c>
-      <c r="B29" s="52" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" s="52" t="s">
-        <v>41</v>
-      </c>
-      <c r="D29" s="51"/>
-      <c r="E29" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F29" s="52"/>
-      <c r="G29" s="51"/>
-    </row>
-    <row r="30" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A30" s="49" t="s">
-        <v>253</v>
-      </c>
-      <c r="B30" s="50" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" s="50" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F30" s="50"/>
-      <c r="G30" s="49"/>
-    </row>
-    <row r="31" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A31" s="51" t="s">
-        <v>254</v>
-      </c>
-      <c r="B31" s="52" t="s">
-        <v>184</v>
-      </c>
-      <c r="C31" s="52" t="s">
-        <v>326</v>
-      </c>
-      <c r="D31" s="51"/>
-      <c r="E31" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F31" s="52"/>
-      <c r="G31" s="51"/>
-    </row>
-    <row r="32" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A32" s="49" t="s">
-        <v>255</v>
-      </c>
-      <c r="B32" s="50" t="s">
-        <v>92</v>
-      </c>
-      <c r="C32" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="D32" s="49"/>
-      <c r="E32" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F32" s="50"/>
-      <c r="G32" s="49"/>
-    </row>
-    <row r="33" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A33" s="51" t="s">
-        <v>256</v>
-      </c>
-      <c r="B33" s="52" t="s">
-        <v>97</v>
-      </c>
-      <c r="C33" s="52" t="s">
-        <v>99</v>
-      </c>
-      <c r="D33" s="51"/>
-      <c r="E33" s="51" t="s">
-        <v>237</v>
-      </c>
-      <c r="F33" s="52"/>
-      <c r="G33" s="51"/>
-    </row>
-    <row r="34" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A34" s="49" t="s">
-        <v>257</v>
-      </c>
-      <c r="B34" s="50" t="s">
-        <v>102</v>
-      </c>
-      <c r="C34" s="50" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="49"/>
-      <c r="E34" s="49" t="s">
-        <v>237</v>
-      </c>
-      <c r="F34" s="50"/>
-      <c r="G34" s="49"/>
-    </row>
-    <row r="36" spans="1:7" ht="43.5" customHeight="1">
-      <c r="A36" s="53" t="s">
-        <v>328</v>
-      </c>
-      <c r="B36" s="53"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
+      <c r="B36" s="69"/>
+      <c r="C36" s="69"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="69"/>
+      <c r="F36" s="69"/>
+      <c r="G36" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/public/files/copyright-schedule-june-v5.xlsx
+++ b/public/files/copyright-schedule-june-v5.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\info\amy\public\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7297F585-9D85-4076-A9CA-6F759A210B5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6ADA9D0-D319-4E3B-AE9F-BE73FED89926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38295" yWindow="2415" windowWidth="13200" windowHeight="20985" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI매칭_프롬프트" sheetId="1" r:id="rId1"/>
     <sheet name="데드라인순" sheetId="6" r:id="rId2"/>
-    <sheet name="6월_업무마스터" sheetId="2" r:id="rId3"/>
-    <sheet name="플랫폼매핑" sheetId="3" r:id="rId4"/>
-    <sheet name="미쟝센_쿼리(베트남팀_데이터)" sheetId="11" r:id="rId5"/>
-    <sheet name="PXG_쿼리" sheetId="7" r:id="rId6"/>
-    <sheet name="매칭_판단기준" sheetId="8" r:id="rId7"/>
-    <sheet name="KPI_검토" sheetId="9" r:id="rId8"/>
-    <sheet name="확인필요_체크리스트" sheetId="5" r:id="rId9"/>
-    <sheet name="목표수량_출처비교" sheetId="4" r:id="rId10"/>
-    <sheet name="정리 전" sheetId="10" r:id="rId11"/>
+    <sheet name="7월_업무마스터" sheetId="12" r:id="rId3"/>
+    <sheet name="6월_업무마스터" sheetId="2" r:id="rId4"/>
+    <sheet name="플랫폼매핑" sheetId="3" r:id="rId5"/>
+    <sheet name="미쟝센_쿼리(베트남팀_데이터)" sheetId="11" r:id="rId6"/>
+    <sheet name="PXG_쿼리" sheetId="7" r:id="rId7"/>
+    <sheet name="매칭_판단 기준" sheetId="8" r:id="rId8"/>
+    <sheet name="KPI_검토" sheetId="9" r:id="rId9"/>
+    <sheet name="확인필요_체크리스트" sheetId="5" r:id="rId10"/>
+    <sheet name="목표수량_출처비교" sheetId="4" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="419">
   <si>
     <t>구분</t>
   </si>
@@ -1050,31 +1051,31 @@
   </si>
   <si>
     <t>18일</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>19일</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>샤넬 (235)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>임시계정. 데이터 없으면 담당자 전달</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매칭리뷰 전체</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>트렐로='전체반영'. 인계서엔 목표 유경님 확인. 미국+저가 (저가 기준 안내 없음)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>보호원26_코스알엑스 (416)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>6월 데드라인</t>
@@ -1121,26 +1122,26 @@
   <si>
     <t>한국: 국내 주요 온라인스토어(NaverStore·11ST·Gmarket·Auction·Coupang 등)
 [기준: #952 ※계약엔 "국내 주요 온라인스토어"로만 명시]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>올영_웨이크메이크 (432)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>조건 메일확인
 ★최종수량 이사님 검토중(승인 전까지 기존값 유지)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>국내: NaverStore·11ST·Gmarket·Auction·Coupang
 동남아: Shopee(MY·SG·PH·VN·TH) · Lazada(MY·SG·PH·VN·TH) · Tokopedia
 미국: Alibaba (배송지·화폐 USD=미국 기준)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>이창엽 이사님 리뷰. / 데이터 엉망 (매칭 가능 데이터 없음.) 500-2900건 실패</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1164,328 +1165,15 @@
       </rPr>
       <t>26.6 스킵</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>브랜드</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">※ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>변경</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>: (Load Item)+(Update Review) → (Load Query)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">에 아래 쿼리 입력 후 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>600</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>건 탐지</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>플랫폼</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">(TT/NB/IG) </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>비율 조정 불필요</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="9"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t>.</t>
-    </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>※ Ai 매칭 활용 시 아래 프롬프트를 (gpt 5.4) 와 함께 사용. (누끼 동일 이미지 매칭)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Segoe UI Emoji"/>
-        <family val="2"/>
-      </rPr>
-      <t>📋</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>저작권</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (SNS </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>탐지ㅣ</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">STORE </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>정기</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>모니터링</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>년</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 6</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>월</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>트렐로</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>목표수량</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>기준</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFC2334D"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>※ 목표수량=트렐로 최종 기준 · 데드라인=전처리스케줄 6월 값 · 담당 브랜드 매월 변동 가능 · ⚠확인필요 ★이사님/담당자 확인 ✅6월 완료표기</t>
@@ -1578,7 +1266,7 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -1727,7 +1415,7 @@
 국내&lt;12,000 / 
 미국&lt;15,000 /
 그 외&lt;10,000원</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>중국: 1688·Taobao·Tmall·Temu·JD·Made-in-China
@@ -1739,16 +1427,16 @@
 필리핀: Shopee·Lazada
 일본: Rakuten·Qoo10·Mercari·Yahoo(jp)·Amazon·AliExpress
 [기준: #952 + 내부 국가별플랫폼표]</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>report_date 미입력. SNS폴로(237). 
 샤넬_저작권(302) 과는 별개.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>트렐로엔 있음. R&amp;R상 406은 '가품'·담당 이창엽. 인수범위 확인</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>중국: 1688·Taobao·Tmall·Temu·JD·Made-in-China
@@ -1761,16 +1449,16 @@
 UAE: Amazon·Noon
 [기준: #890 LG생활건강 8개국 + 내부표]
 ★계약 재개/연장 확인(트렐로 26.6 수량배정)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>▶ 운영 메모: 위 특징에 해당하면 O/X 판정하지 말고 △로 분류 → 별도 보관. 
 신규 애매 유형 발견 시 이 표에 행 추가. 데이터 부족 시 기준 확인 후 「확정일·결정(O/X)·결정자」 열을 덧붙여 이력화 권장.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>주요 의류가 아닌 소품/부위의 로고 → 탐지 범위에 포함하는지 미정</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>브랜드(번호)</t>
@@ -1839,15 +1527,15 @@
 - 제품 표면의 질감과 세부 디테일
 - 배경에 있는 소품이나 그래픽 요소의 위치</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>▶ 이사님께서 변동 발생 시 트렐로 카드 코멘트 1줄 (예: "6/20 피지오겔 제외") 입력 → 엑셀 갱신 → 마감 당일 통보 방지를 위해 변동 시 바로 공유 필요.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>LOAD QUERY (전문)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>LOAD 입력값 ①</t>
@@ -1866,21 +1554,21 @@
   </si>
   <si>
     <t>R&amp;R상 해당 해외 '모조품' 행 실무자에 '심지은' 기재됨.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>현재 지민님 진행 중 — 확인 필요</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>트렐로엔 인수목록에 있으나 R&amp;R상 해외는 '가품'·담당 이창엽. 
 해외 저작권까지 받는 게 맞는지</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>트렐로='저작권 1000~2000건' vs 인수인계서='1차 전처리만'. 
 탐지까지인지 전처리만인지 확정</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>~150건</t>
@@ -1899,7 +1587,7 @@
   </si>
   <si>
     <t>일치 여부</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -2216,11 +1904,11 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>확인 필요</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -2266,7 +1954,7 @@
       </rPr>
       <t>최종수량 이사님 검토중(승인 전까지 기존값 유지)</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -2547,20 +2235,16 @@
   </si>
   <si>
     <t>SNS - PXG(212) 데이터 분류 — (Load Query) 방식</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>제외: 화이트 셀러 (mall_name 11곳)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>※ 변동 사항 (제외/추가/필요 수량 변경) 발생 시 트렐로 카드를 단일 출처로. 구두 전달 금지 
 — 확정(이사님) 칸이 채워져야 검토 완료. 빈칸=미검토. 안내 경로: 이사님→팀장님+알바생</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>생로랑 (223)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -2670,103 +2354,97 @@
 (신규 / 실패) 모두 선택된 상태에서는 (실패) 검수된 데이터가 우선 노출되어
 이미 실패로 등록한 데이터를 다시 한번 검수하는 형태가 되므로 매우 중요. (2026-06-22) 퇴근 전 전달 받아 이후부터 적용.</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>SNS-PXG (TT/NB/IG)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>SNS-chanel (IG)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>SNS-kering (IG)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>※ 탐지 대상인지 아직 정해지지 않은 애매 케이스의 특징 정리. 담당자별로 기준 다름 → 헷갈릴 때 "보류 케이스"로 분류하고 별도 보관. 
 데이터 부족 시 기준 확정 후 그때부터 일괄 적용.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>최종 100건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>[PXG] 는 메인 아이템 위주로, 골프 용품 모두 매칭
-[샤넬] 메인 아니더라도 모두 매칭
-*브랜드별로 달라서-</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>상의·하의 등 착용은 다른 브랜드(예: 상의 anew·하의 PXG)인데, 
 이미지 옆에 텍스트로 탐지 브랜드명(예: anew)이 적힌 경우</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>로고가 상의·하의가 아닌 부위에 있는 경우
 (예: 양말에 로고, 드라이버 등)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>공식몰에서 사용하는 모델 사진이지만, 
 로고 플레이(로고 전면 노출 디자인)가 없는 옷인 경우</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>여러 아이템이 함께 노출된 이미지에서,
 탐지 브랜드가 메인 아이템이 아니거나 메인 여부가 불명확한 경우</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>브랜드가 이미지에 있긴 하나 "주된 상품"인지 애매 
 → 메인 아이템 판단 기준 자체가 미정</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>공식몰 출처 + 로고 비노출
 → 도용/침해로 볼지, 정상 사용으로 볼지 미정</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[갱신] 피지오겔/더후/더페이스샵(411/412/413) 
 — 계약 재개/연장 확인 필요,
 트렐로 26.6 최종수량(100/100/150) 배정·복원</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>▶ 매핑 규칙: 각 브랜드 계약 국가 ∩ 본 기준표 = 탐지 플랫폼. 
 계약 국가에 없는 플랫폼은 제외(예: 중국만 탐지 시 Shopee=동남아 전용→제외).
 계약에 플랫폼이 명시된 건은 계약 명시 우선, 미명시 건만 본 표로 보충.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>AliExpress · AliExpress(중국) · Alibaba(중국) · DHgate(중국) · Ubuy(쿠웨이트)</t>
   </si>
   <si>
     <t>매주 목요일까지 600건 리뷰</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>PXG (212)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>6월 데드라인</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[AMCR] 가품 데이터 수집 및 탐지 (크롤링-5일/탐지-7일)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[샤넬] SNS 가품 계정 검수 및 크롤링 (화/금)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[미쟝센] 수동 입력 (20일)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -2915,59 +2593,55 @@
       </rPr>
       <t>)</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[닥터마틴] 수동 입력</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[루미큐브] 5월 수동입력</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[보호원-에스엠엔터] 상표 현황 조회</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[엘지이노텍] 부경법 위반 데이터 탐지</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[올리브영] 3월 수동 입력</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[우봉고] 수동 입력</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>전체 반영</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>(6월) 전체 반영</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>추후 설명</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>인수 시점 확인</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>추후 별도 설명 예정 (6월 패스)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>다음 주 재확인 필요 (변동 예정)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
-  </si>
-  <si>
-    <t>LG 폴더폰= 테더링용 (pw 990330)</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3009,254 +2683,254 @@
 'golfbrandy_official'
 )</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>정리중</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>20일</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>07/10 보고</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>6/30 보고</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매주 목요일</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매월 5~20일 주간</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>200건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매칭/수량</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매칭 200건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>최종 100-150건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매칭 300건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매칭 50-100건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매칭 200-300건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매칭 1000건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매칭 800건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>최종 500-1000건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매칭 2000-4000건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>최종 1000~2000건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[SNS-PXG] (212)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[SNS-kering] 보테가베네타 (224)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[SNS-kering] 생로랑 (223)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[SNS-kering] 발렌시아가 (222)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[SNS-kering] 구찌 (190)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>25일</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매주 금요일</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매주 수요일</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>30-50건/주</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>600건/주</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매칭 1000-2000건</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>설화수_국내 (247)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>60-100건/주</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>24일</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[SNS-kering] 폴로 (237)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[SNS-kering] 구찌 (190) 발렌시아가 (222) 생로랑 (223) 보테가베네타 (224) 폴로 (237)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[SNS-kering] 구찌 (190) 1차 매칭</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[KT&amp;G] SNS 데이터 추가 현황 확인 &lt;매월 7일&gt;</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[샤넬] SNS 데이터 추가 현황 확인 &lt;매월 말일&gt;</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[KT&amp;G] SNS 수동 입력 (9일)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>샤넬_저작권 (255) 
 Update : Watch_no (16493) 입력</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>최종 건수/목표 수량
 (트렐로) (매칭은 2배)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>report_date 미입력. 
 데이터 1500개↓시 제준님께 안내.
 (TT 400/NB 200/IG는 보통 데이터 소량 존재)
 TT/NB/IG 크롤링 비율 맞춰서 진행 (x)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>주당 약 600건
 (TT400/NB200/IG전체)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>수동입력 (목표 50개↑)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>플랫폼별 비율 골고루.
 가격 조건 메일 공유 예정</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>report_date 미입력.
 완료 시 트렐로 코멘트 '작업 완료(번호)'.
 OOTD 제외→진혁님</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>네이버스토어 50%↑. 부족 시 추가 매칭</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Company no. 비일치. 
 트렐로·스케줄 432, but R&amp;R 428. 추후 확인
 (Matching Review 웹에는 432 데이터만 존재.)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[가히] 수동입력」 트렐로 참고
 (목표 50개↑ but 실제로는 많지 않음.)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>Report_date 입력 시 Watch_no. (16493) 입력
 [STORE-샤넬] (255)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>샤넬_저작권 (255)
 Watch_no. (16493) 필수 기입</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>50-100건/주 (5-20일 사이)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>[SNS-샤넬] (235)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>매주 월요일</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>50-100건/주</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>약 60건 (?)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>약 120건 (?)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>600건/주
 (TT:NB:IG =400:200:All)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>STORE - 미쟝센 (396) 베트남팀 수집 데이터 분류 — (Load Query) 방식</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3319,34 +2993,34 @@
       </rPr>
       <t>입력</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>미정</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>REPORT_DATE: 당월 언제든 (2026-00-00 형식)</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>REPORT_DATE: 당월 언제든 (2026-00-00 형식)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>-</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <t>where watch_no = 16129
 and report_date is null
 and regdate &gt;= '2026-06-01'
 and regdate &lt; '2026-07-01'</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>(Copyright no. 정리 필요) 새 엑셀에 따로 기입 후 제준님에게 전달</t>
-    <phoneticPr fontId="22" type="noConversion"/>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3556,15 +3230,15 @@
       <t>)
 http://console.faikerz.com/Admin/CopyrightImage/List?condition=COMPANY_NO&amp;keyword=396&amp;pageNo=1</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>New Sheet for Copyright_no.</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <t>※ Schedule Ai 활용 시 위 프롬프트를 (gpt 5.4 mini) 와 함께 사용. (누끼 동일 이미지 매칭)</t>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3706,7 +3380,673 @@
       </rPr>
       <t>/ sk, kt …</t>
     </r>
-    <phoneticPr fontId="17" type="noConversion"/>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>※ 변경: (Load Item)+(Update Review) → (Load Query)에</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>아래</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>쿼리</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>입력</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>후</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>600건</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐지. 플랫폼(TT/NB/IG) 비율</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>조정</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>불필요.</t>
+    </r>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>화이트 셀러 (mall_name 11곳)</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notes</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>1) 이번 주만 하루 빨리 마감 필요
+2) 골프채 제외 (정품 다수)
+3) 부족한 틱톡 데이터 보충 방법
+Item Review (틱톡만 선택)
+*Company_no: 212
+*(2026-02-01) - (2026-03-01)
+*한 달 간격으로 불러오기
+4) Upload 시 입력 정보
+[SNS]
+*report_date: 당월 해당 주차 수요일
+*infringement_type: 1 (데드카피)
+[Store]
+*report_date: 당월 10일
+*infringement_type: 5 (저작권)</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>[PXG] 는 메인 아이템 위주로, 골프 용품 모두 매칭
+[샤넬] 메인 아니더라도 모두 매칭
+*브랜드별로 달라서 차례로 확인 필요</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>5) Upload 시 입력 정보 업데이트
+[SNS]
+*report_date: 당월 당주 (수요일)
+*infringement_type: 1 (데드카피)
+[Store]
+*report_date: 당월 (10일)
+*infringement_type: 5 (저작권)</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>⏭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">KPI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>재확인 필요</t>
+    </r>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>조건 메일 확인 필요
+(현재 미수신)
+★최종 수량 검토 필요</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저작권</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (SNS </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐지ㅣ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">STORE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모니터링</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>월</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>트렐로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목표 수량</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>📋</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>저작권</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (SNS </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐지ㅣ</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">STORE </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>정기</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모니터링</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 6</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>월</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>트렐로</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>목표 수량</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>기준</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFC2334D"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="21" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -3804,12 +4144,6 @@
       <name val="맑은 고딕"/>
       <family val="2"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <name val="Noto Sans CJK SC"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3998,8 +4332,13 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4102,8 +4441,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -4185,15 +4536,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="5" tint="0.59999389629810485"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="5" tint="0.59999389629810485"/>
       </left>
@@ -4242,7 +4584,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -4258,7 +4600,7 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4268,13 +4610,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4298,7 +4640,7 @@
     <xf numFmtId="0" fontId="8" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4322,7 +4664,7 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4345,13 +4687,13 @@
     <xf numFmtId="0" fontId="9" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4363,12 +4705,9 @@
     <xf numFmtId="0" fontId="6" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4379,46 +4718,16 @@
     <xf numFmtId="0" fontId="6" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4427,10 +4736,10 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4442,26 +4751,68 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="40" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="30" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -4469,13 +4820,13 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4487,17 +4838,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4778,7 +5120,7 @@
     <row r="1" spans="1:9" ht="35" customHeight="1">
       <c r="A1" s="5"/>
       <c r="B1" s="9" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="5"/>
@@ -4791,7 +5133,7 @@
     <row r="2" spans="1:9">
       <c r="A2" s="5"/>
       <c r="B2" s="8" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -4814,22 +5156,192 @@
     </row>
     <row r="4" spans="1:9" ht="400">
       <c r="B4" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="8" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="5" customWidth="1"/>
+    <col min="2" max="2" width="35.58203125" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="62" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="30" customHeight="1">
+      <c r="A1" s="89" t="s">
+        <v>300</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+    </row>
+    <row r="2" spans="1:4" ht="27.75" customHeight="1">
+      <c r="A2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="35" customHeight="1">
+      <c r="A3" s="3">
+        <v>1</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="35" customHeight="1">
+      <c r="A4" s="3">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="20" customHeight="1">
+      <c r="A5" s="3">
+        <v>3</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="20" customHeight="1">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="20" customHeight="1">
+      <c r="A7" s="3">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="20" customHeight="1">
+      <c r="A8" s="3">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="20" customHeight="1">
+      <c r="A9" s="3">
+        <v>7</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="20" customHeight="1">
+      <c r="A10" s="3">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="150" customHeight="1">
+      <c r="A11" s="3">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <phoneticPr fontId="16" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="66" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -4844,13 +5356,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="71" t="s">
-        <v>298</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="A1" s="89" t="s">
+        <v>296</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
+      <c r="E1" s="61"/>
     </row>
     <row r="2" spans="1:5" ht="27.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -4863,7 +5375,7 @@
         <v>134</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -4874,10 +5386,10 @@
         <v>29</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D3" s="40" t="s">
         <v>135</v>
@@ -4894,7 +5406,7 @@
         <v>248</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D4" s="40" t="s">
         <v>135</v>
@@ -4911,7 +5423,7 @@
         <v>248</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D5" s="40" t="s">
         <v>135</v>
@@ -4928,7 +5440,7 @@
         <v>248</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D6" s="40" t="s">
         <v>135</v>
@@ -4945,7 +5457,7 @@
         <v>248</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D7" s="40" t="s">
         <v>135</v>
@@ -4959,10 +5471,10 @@
         <v>21</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="D8" s="41" t="s">
         <v>138</v>
@@ -4976,45 +5488,25 @@
         <v>140</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D9" s="40" t="s">
         <v>135</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="76" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8FC1FD9-41DC-446F-A7D5-796DDFAA5FA6}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17"/>
-  <cols>
-    <col min="1" max="1" width="100.58203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="44" t="s">
-        <v>343</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="22" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5033,16 +5525,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="56" t="s">
-        <v>303</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
+      <c r="A1" s="60" t="s">
+        <v>301</v>
+      </c>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
+      <c r="D1" s="61"/>
     </row>
     <row r="2" spans="1:5" ht="27.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -5054,7 +5546,7 @@
         <v>163</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" customHeight="1">
@@ -5071,7 +5563,7 @@
         <v>248</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17" customHeight="1">
@@ -5088,7 +5580,7 @@
         <v>248</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17" customHeight="1">
@@ -5105,7 +5597,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="17" customHeight="1">
@@ -5119,10 +5611,10 @@
         <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="17" customHeight="1">
@@ -5130,21 +5622,21 @@
         <v>244</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>239</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="17" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>41</v>
@@ -5161,7 +5653,7 @@
     </row>
     <row r="9" spans="1:5" ht="17" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>46</v>
@@ -5178,7 +5670,7 @@
     </row>
     <row r="10" spans="1:5" ht="17" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>48</v>
@@ -5212,7 +5704,7 @@
     </row>
     <row r="12" spans="1:5" ht="17" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>164</v>
@@ -5238,10 +5730,10 @@
         <v>77</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="17" customHeight="1">
@@ -5255,10 +5747,10 @@
         <v>20</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="E14" s="39" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="17" customHeight="1">
@@ -5266,7 +5758,7 @@
         <v>247</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C15" s="23" t="s">
         <v>20</v>
@@ -5275,7 +5767,7 @@
         <v>248</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="17" customHeight="1">
@@ -5292,7 +5784,7 @@
         <v>248</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="17" customHeight="1">
@@ -5326,7 +5818,7 @@
         <v>60</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="17" customHeight="1">
@@ -5343,7 +5835,7 @@
         <v>63</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="17" customHeight="1">
@@ -5360,7 +5852,7 @@
         <v>66</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="17" customHeight="1">
@@ -5377,7 +5869,7 @@
         <v>66</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="17" customHeight="1">
@@ -5394,7 +5886,7 @@
         <v>33</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="17" customHeight="1">
@@ -5411,7 +5903,7 @@
         <v>33</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="17" customHeight="1">
@@ -5428,7 +5920,7 @@
         <v>60</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="17" customHeight="1">
@@ -5442,7 +5934,7 @@
         <v>77</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E25" s="23" t="s">
         <v>86</v>
@@ -5450,7 +5942,7 @@
     </row>
     <row r="26" spans="1:5" ht="17" customHeight="1">
       <c r="A26" s="23" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B26" s="23" t="s">
         <v>88</v>
@@ -5459,7 +5951,7 @@
         <v>77</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="E26" s="23" t="s">
         <v>86</v>
@@ -5467,135 +5959,135 @@
     </row>
     <row r="27" spans="1:5" ht="35" customHeight="1">
       <c r="A27" s="23" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="C27" s="23" t="s">
         <v>20</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="17" customHeight="1">
-      <c r="A28" s="50"/>
-      <c r="B28" s="51"/>
-      <c r="C28" s="51"/>
-      <c r="D28" s="51"/>
-      <c r="E28" s="52"/>
+      <c r="A28" s="62"/>
+      <c r="B28" s="63"/>
+      <c r="C28" s="63"/>
+      <c r="D28" s="63"/>
+      <c r="E28" s="64"/>
     </row>
     <row r="29" spans="1:5" ht="17" customHeight="1">
       <c r="A29" s="23" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="C29" s="23" t="s">
         <v>239</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="17" customHeight="1">
       <c r="A30" s="23" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C30" s="23" t="s">
         <v>239</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="35" customHeight="1">
       <c r="A31" s="23" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C31" s="23" t="s">
         <v>239</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="50" customHeight="1">
       <c r="A32" s="23" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="C32" s="23" t="s">
         <v>239</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="17" customHeight="1">
-      <c r="A33" s="50"/>
-      <c r="B33" s="51"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
-      <c r="E33" s="52"/>
+      <c r="A33" s="62"/>
+      <c r="B33" s="63"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="64"/>
     </row>
     <row r="34" spans="1:5" ht="17" customHeight="1">
       <c r="A34" s="23" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C34" s="23" t="s">
         <v>239</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="17" customHeight="1">
       <c r="A35" s="23" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="C35" s="23" t="s">
         <v>239</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="17" customHeight="1">
@@ -5603,16 +6095,16 @@
         <v>240</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C36" s="23" t="s">
         <v>239</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="17" customHeight="1">
@@ -5620,236 +6112,226 @@
         <v>240</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="C37" s="23" t="s">
         <v>239</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="17" customHeight="1">
       <c r="A38" s="23" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C38" s="23" t="s">
         <v>239</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="17" customHeight="1">
-      <c r="A39" s="50"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="52"/>
+      <c r="A39" s="62"/>
+      <c r="B39" s="63"/>
+      <c r="C39" s="63"/>
+      <c r="D39" s="63"/>
+      <c r="E39" s="64"/>
     </row>
     <row r="40" spans="1:5" ht="30" customHeight="1">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="69" t="s">
+        <v>326</v>
+      </c>
+      <c r="B40" s="69"/>
+      <c r="C40" s="69"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="69"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="68" t="s">
+        <v>340</v>
+      </c>
+      <c r="B41" s="68"/>
+      <c r="C41" s="68"/>
+      <c r="D41" s="68"/>
+      <c r="E41" s="68"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="59" t="s">
+        <v>324</v>
+      </c>
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="B43" s="59"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="59" t="s">
+        <v>377</v>
+      </c>
+      <c r="B44" s="59"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="59" t="s">
+        <v>325</v>
+      </c>
+      <c r="B45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="65" t="s">
+        <v>327</v>
+      </c>
+      <c r="B46" s="66"/>
+      <c r="C46" s="66"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="67"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="65" t="s">
+        <v>328</v>
+      </c>
+      <c r="B47" s="66"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="67"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="65" t="s">
         <v>330</v>
       </c>
-      <c r="B40" s="54"/>
-      <c r="C40" s="54"/>
-      <c r="D40" s="54"/>
-      <c r="E40" s="54"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="53" t="s">
-        <v>345</v>
-      </c>
-      <c r="B41" s="53"/>
-      <c r="C41" s="53"/>
-      <c r="D41" s="53"/>
-      <c r="E41" s="53"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="55" t="s">
-        <v>328</v>
-      </c>
-      <c r="B42" s="55"/>
-      <c r="C42" s="55"/>
-      <c r="D42" s="55"/>
-      <c r="E42" s="55"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="55" t="s">
-        <v>327</v>
-      </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="55" t="s">
-        <v>382</v>
-      </c>
-      <c r="B44" s="55"/>
-      <c r="C44" s="55"/>
-      <c r="D44" s="55"/>
-      <c r="E44" s="55"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="48" t="s">
+      <c r="B48" s="66"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="67"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="65" t="s">
+        <v>331</v>
+      </c>
+      <c r="B49" s="66"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="67"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="65" t="s">
+        <v>332</v>
+      </c>
+      <c r="B50" s="66"/>
+      <c r="C50" s="66"/>
+      <c r="D50" s="66"/>
+      <c r="E50" s="67"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="65" t="s">
         <v>329</v>
       </c>
-      <c r="B45" s="48"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="84" t="s">
-        <v>331</v>
-      </c>
-      <c r="B46" s="85"/>
-      <c r="C46" s="85"/>
-      <c r="D46" s="85"/>
-      <c r="E46" s="86"/>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="84" t="s">
-        <v>332</v>
-      </c>
-      <c r="B47" s="85"/>
-      <c r="C47" s="85"/>
-      <c r="D47" s="85"/>
-      <c r="E47" s="86"/>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="84" t="s">
-        <v>334</v>
-      </c>
-      <c r="B48" s="85"/>
-      <c r="C48" s="85"/>
-      <c r="D48" s="85"/>
-      <c r="E48" s="86"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="84" t="s">
-        <v>335</v>
-      </c>
-      <c r="B49" s="85"/>
-      <c r="C49" s="85"/>
-      <c r="D49" s="85"/>
-      <c r="E49" s="86"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="84" t="s">
-        <v>336</v>
-      </c>
-      <c r="B50" s="85"/>
-      <c r="C50" s="85"/>
-      <c r="D50" s="85"/>
-      <c r="E50" s="86"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="84" t="s">
-        <v>333</v>
-      </c>
-      <c r="B51" s="85"/>
-      <c r="C51" s="85"/>
-      <c r="D51" s="85"/>
-      <c r="E51" s="86"/>
+      <c r="B51" s="66"/>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="67"/>
     </row>
     <row r="52" spans="1:5">
-      <c r="A52" s="55" t="s">
-        <v>380</v>
-      </c>
-      <c r="B52" s="55"/>
-      <c r="C52" s="55"/>
-      <c r="D52" s="55"/>
-      <c r="E52" s="55"/>
+      <c r="A52" s="59" t="s">
+        <v>375</v>
+      </c>
+      <c r="B52" s="59"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
     </row>
     <row r="53" spans="1:5">
-      <c r="A53" s="55" t="s">
-        <v>381</v>
-      </c>
-      <c r="B53" s="55"/>
-      <c r="C53" s="55"/>
-      <c r="D53" s="55"/>
-      <c r="E53" s="55"/>
+      <c r="A53" s="59" t="s">
+        <v>376</v>
+      </c>
+      <c r="B53" s="59"/>
+      <c r="C53" s="59"/>
+      <c r="D53" s="59"/>
+      <c r="E53" s="59"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="49"/>
-      <c r="B54" s="49"/>
-      <c r="C54" s="49"/>
-      <c r="D54" s="49"/>
-      <c r="E54" s="49"/>
+      <c r="A54" s="58"/>
+      <c r="B54" s="58"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="49"/>
-      <c r="B55" s="49"/>
-      <c r="C55" s="49"/>
-      <c r="D55" s="49"/>
-      <c r="E55" s="49"/>
+      <c r="A55" s="58"/>
+      <c r="B55" s="58"/>
+      <c r="C55" s="58"/>
+      <c r="D55" s="58"/>
+      <c r="E55" s="58"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="49"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="49"/>
-      <c r="D56" s="49"/>
-      <c r="E56" s="49"/>
+      <c r="A56" s="58"/>
+      <c r="B56" s="58"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="58"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="49"/>
-      <c r="B57" s="49"/>
-      <c r="C57" s="49"/>
-      <c r="D57" s="49"/>
-      <c r="E57" s="49"/>
+      <c r="A57" s="58"/>
+      <c r="B57" s="58"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="58"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="49"/>
-      <c r="B58" s="49"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
+      <c r="A58" s="58"/>
+      <c r="B58" s="58"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="49"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-      <c r="E59" s="49"/>
+      <c r="A59" s="58"/>
+      <c r="B59" s="58"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+      <c r="E59" s="58"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="49"/>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="49"/>
+      <c r="A60" s="58"/>
+      <c r="B60" s="58"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="49"/>
-      <c r="B61" s="49"/>
-      <c r="C61" s="49"/>
-      <c r="D61" s="49"/>
-      <c r="E61" s="49"/>
+      <c r="A61" s="58"/>
+      <c r="B61" s="58"/>
+      <c r="C61" s="58"/>
+      <c r="D61" s="58"/>
+      <c r="E61" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A57:E57"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A53:E53"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A51:E51"/>
-    <mergeCell ref="A52:E52"/>
-    <mergeCell ref="A54:E54"/>
-    <mergeCell ref="A55:E55"/>
-    <mergeCell ref="A56:E56"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A60:E60"/>
     <mergeCell ref="A61:E61"/>
@@ -5866,15 +6348,25 @@
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A49:E49"/>
     <mergeCell ref="A50:E50"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A51:E51"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A56:E56"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="62" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD27F411-16CA-4E53-BACC-2872E0D6C15C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5890,30 +6382,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="50" customHeight="1">
-      <c r="A1" s="64" t="s">
-        <v>261</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
+      <c r="A1" s="53" t="s">
+        <v>417</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A2" s="65" t="s">
-        <v>262</v>
-      </c>
-      <c r="B2" s="65"/>
-      <c r="C2" s="65"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="65"/>
-      <c r="F2" s="65"/>
-      <c r="G2" s="65"/>
-      <c r="H2" s="65"/>
-      <c r="I2" s="65"/>
+      <c r="A2" s="54" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
     </row>
     <row r="3" spans="1:9" ht="50" customHeight="1">
       <c r="A3" s="11" t="s">
@@ -5932,7 +6424,7 @@
         <v>238</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="G3" s="11" t="s">
         <v>4</v>
@@ -5952,7 +6444,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>8</v>
@@ -5968,7 +6460,7 @@
         <v>241</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="50" customHeight="1">
@@ -5979,7 +6471,7 @@
         <v>10</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D5" s="13" t="s">
         <v>11</v>
@@ -6003,10 +6495,10 @@
         <v>239</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D6" s="13" t="s">
         <v>11</v>
@@ -6033,7 +6525,7 @@
         <v>13</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D7" s="13" t="s">
         <v>11</v>
@@ -6060,7 +6552,7 @@
         <v>14</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D8" s="13" t="s">
         <v>11</v>
@@ -6076,7 +6568,7 @@
         <v>241</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="50" customHeight="1">
@@ -6087,10 +6579,10 @@
         <v>233</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>244</v>
@@ -6111,10 +6603,10 @@
         <v>239</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D10" s="13" t="s">
         <v>17</v>
@@ -6123,14 +6615,14 @@
         <v>18</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="12" t="s">
         <v>241</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="50" customHeight="1">
@@ -6138,7 +6630,7 @@
         <v>20</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C11" s="13" t="s">
         <v>22</v>
@@ -6157,7 +6649,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="50" customHeight="1">
@@ -6227,7 +6719,7 @@
         <v>247</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="14" t="s">
@@ -6252,7 +6744,7 @@
         <v>231</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="14" t="s">
@@ -6277,7 +6769,7 @@
         <v>231</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="14" t="s">
@@ -6302,14 +6794,14 @@
         <v>247</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G17" s="13"/>
       <c r="H17" s="14" t="s">
         <v>39</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="100" customHeight="1">
@@ -6419,13 +6911,13 @@
         <v>42</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="H21" s="15" t="s">
         <v>51</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="100" customHeight="1">
@@ -6476,10 +6968,10 @@
       </c>
       <c r="G23" s="13"/>
       <c r="H23" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="I23" s="13" t="s">
         <v>266</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="170" customHeight="1">
@@ -6503,7 +6995,7 @@
       </c>
       <c r="G24" s="13"/>
       <c r="H24" s="17" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="I24" s="13" t="s">
         <v>61</v>
@@ -6591,6 +7083,1046 @@
       </c>
     </row>
     <row r="28" spans="1:9" ht="180" customHeight="1">
+      <c r="A28" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="H28" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="I28" s="21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="180" customHeight="1">
+      <c r="A29" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="H29" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="180" customHeight="1">
+      <c r="A30" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" s="21" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="100" customHeight="1">
+      <c r="A31" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="I31" s="47" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="100" customHeight="1">
+      <c r="A32" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="H32" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="I32" s="47" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="100" customHeight="1">
+      <c r="A33" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="G33" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="H33" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="I33" s="22"/>
+    </row>
+    <row r="34" spans="1:9" ht="100" customHeight="1">
+      <c r="A34" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="22" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34" s="22" t="s">
+        <v>251</v>
+      </c>
+      <c r="F34" s="22" t="s">
+        <v>86</v>
+      </c>
+      <c r="G34" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="H34" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="I34" s="22" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="19.5" customHeight="1"/>
+    <row r="36" spans="1:9" ht="35" customHeight="1">
+      <c r="A36" s="56" t="s">
+        <v>262</v>
+      </c>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+    </row>
+    <row r="37" spans="1:9" ht="30" customHeight="1">
+      <c r="A37" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
+    </row>
+    <row r="38" spans="1:9" ht="30" customHeight="1">
+      <c r="A38" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+    </row>
+    <row r="39" spans="1:9" ht="50" customHeight="1">
+      <c r="A39" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+    </row>
+    <row r="40" spans="1:9" ht="30" customHeight="1">
+      <c r="A40" s="55" t="s">
+        <v>92</v>
+      </c>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+    </row>
+    <row r="41" spans="1:9" ht="75" customHeight="1">
+      <c r="A41" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="B41" s="51"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+    </row>
+    <row r="42" spans="1:9" ht="160" customHeight="1">
+      <c r="A42" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="B42" s="51"/>
+      <c r="C42" s="51"/>
+      <c r="D42" s="51"/>
+      <c r="E42" s="51"/>
+      <c r="F42" s="51"/>
+      <c r="G42" s="51"/>
+      <c r="H42" s="51"/>
+      <c r="I42" s="51"/>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="49"/>
+      <c r="B43" s="50"/>
+      <c r="C43" s="50"/>
+      <c r="D43" s="50"/>
+      <c r="E43" s="50"/>
+      <c r="F43" s="50"/>
+      <c r="G43" s="50"/>
+      <c r="H43" s="50"/>
+      <c r="I43" s="50"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A43:I43"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="A39:I39"/>
+  </mergeCells>
+  <phoneticPr fontId="21" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="20" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:I42"/>
+  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17"/>
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="7" width="18" customWidth="1"/>
+    <col min="8" max="9" width="35.58203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="50" customHeight="1">
+      <c r="A1" s="53" t="s">
+        <v>418</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+    </row>
+    <row r="2" spans="1:9" ht="31.5" customHeight="1">
+      <c r="A2" s="54" t="s">
+        <v>260</v>
+      </c>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="54"/>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+    </row>
+    <row r="3" spans="1:9" ht="50" customHeight="1">
+      <c r="A3" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="50" customHeight="1">
+      <c r="A4" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="13"/>
+      <c r="H4" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="50" customHeight="1">
+      <c r="A5" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="13"/>
+      <c r="H5" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="50" customHeight="1">
+      <c r="A6" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="50" customHeight="1">
+      <c r="A7" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="13"/>
+      <c r="H7" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="50" customHeight="1">
+      <c r="A8" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="F8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50" customHeight="1">
+      <c r="A9" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>307</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>345</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="100" customHeight="1">
+      <c r="A10" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>306</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50" customHeight="1">
+      <c r="A11" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="13"/>
+      <c r="H11" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50" customHeight="1">
+      <c r="A12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="13"/>
+    </row>
+    <row r="13" spans="1:9" ht="100" customHeight="1">
+      <c r="A13" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="13"/>
+      <c r="H13" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" spans="1:9" ht="100" customHeight="1">
+      <c r="A14" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" spans="1:9" ht="100" customHeight="1">
+      <c r="A15" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G15" s="13"/>
+      <c r="H15" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" spans="1:9" ht="100" customHeight="1">
+      <c r="A16" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="I16" s="13"/>
+    </row>
+    <row r="17" spans="1:9" ht="100" customHeight="1">
+      <c r="A17" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="G17" s="13"/>
+      <c r="H17" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="100" customHeight="1">
+      <c r="A18" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="F18" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="100" customHeight="1">
+      <c r="A19" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="100" customHeight="1">
+      <c r="A20" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="100" customHeight="1">
+      <c r="A21" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>244</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="100" customHeight="1">
+      <c r="A22" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="170" customHeight="1">
+      <c r="A23" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="13"/>
+      <c r="H23" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="170" customHeight="1">
+      <c r="A24" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="13"/>
+      <c r="H24" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="50" customHeight="1">
+      <c r="A25" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F25" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="13"/>
+      <c r="H25" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="50" customHeight="1">
+      <c r="A26" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="13"/>
+      <c r="H26" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="50" customHeight="1">
+      <c r="A27" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="180" customHeight="1">
       <c r="A28" s="18" t="s">
         <v>52</v>
       </c>
@@ -6613,7 +8145,7 @@
         <v>72</v>
       </c>
       <c r="H28" s="18" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="I28" s="21" t="s">
         <v>256</v>
@@ -6694,16 +8226,16 @@
         <v>250</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="H31" s="22" t="s">
         <v>255</v>
       </c>
-      <c r="I31" s="87" t="s">
-        <v>392</v>
+      <c r="I31" s="47" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="100" customHeight="1">
@@ -6731,8 +8263,8 @@
       <c r="H32" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="I32" s="87" t="s">
-        <v>388</v>
+      <c r="I32" s="47" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="100" customHeight="1">
@@ -6752,10 +8284,10 @@
         <v>243</v>
       </c>
       <c r="F33" s="22" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G33" s="22" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="H33" s="22" t="s">
         <v>87</v>
@@ -6782,119 +8314,107 @@
         <v>86</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="H34" s="22" t="s">
         <v>89</v>
       </c>
       <c r="I34" s="22" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="19.5" customHeight="1"/>
     <row r="36" spans="1:9" ht="35" customHeight="1">
-      <c r="A36" s="67" t="s">
-        <v>264</v>
-      </c>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
+      <c r="A36" s="56" t="s">
+        <v>262</v>
+      </c>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
     </row>
     <row r="37" spans="1:9" ht="30" customHeight="1">
-      <c r="A37" s="66" t="s">
+      <c r="A37" s="55" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="66"/>
-      <c r="C37" s="66"/>
-      <c r="D37" s="66"/>
-      <c r="E37" s="66"/>
-      <c r="F37" s="66"/>
-      <c r="G37" s="66"/>
-      <c r="H37" s="66"/>
-      <c r="I37" s="66"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="55"/>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="55"/>
+      <c r="I37" s="55"/>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1">
-      <c r="A38" s="66" t="s">
+      <c r="A38" s="55" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="66"/>
-      <c r="C38" s="66"/>
-      <c r="D38" s="66"/>
-      <c r="E38" s="66"/>
-      <c r="F38" s="66"/>
-      <c r="G38" s="66"/>
-      <c r="H38" s="66"/>
-      <c r="I38" s="66"/>
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="55"/>
+      <c r="E38" s="55"/>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
     </row>
     <row r="39" spans="1:9" ht="50" customHeight="1">
-      <c r="A39" s="63" t="s">
-        <v>413</v>
-      </c>
-      <c r="B39" s="63"/>
-      <c r="C39" s="63"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="63"/>
-      <c r="F39" s="63"/>
-      <c r="G39" s="63"/>
-      <c r="H39" s="63"/>
-      <c r="I39" s="63"/>
+      <c r="A39" s="52" t="s">
+        <v>408</v>
+      </c>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
     </row>
     <row r="40" spans="1:9" ht="30" customHeight="1">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="55" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="66"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="66"/>
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="55"/>
+      <c r="E40" s="55"/>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
     </row>
     <row r="41" spans="1:9" ht="75" customHeight="1">
-      <c r="A41" s="62" t="s">
-        <v>308</v>
-      </c>
-      <c r="B41" s="62"/>
-      <c r="C41" s="62"/>
-      <c r="D41" s="62"/>
-      <c r="E41" s="62"/>
-      <c r="F41" s="62"/>
-      <c r="G41" s="62"/>
-      <c r="H41" s="62"/>
-      <c r="I41" s="62"/>
+      <c r="A41" s="51" t="s">
+        <v>305</v>
+      </c>
+      <c r="B41" s="51"/>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="60"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
-    </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="58"/>
-      <c r="B43" s="59"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-      <c r="F43" s="59"/>
-      <c r="G43" s="59"/>
-      <c r="H43" s="59"/>
-      <c r="I43" s="59"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="50"/>
+      <c r="C42" s="50"/>
+      <c r="D42" s="50"/>
+      <c r="E42" s="50"/>
+      <c r="F42" s="50"/>
+      <c r="G42" s="50"/>
+      <c r="H42" s="50"/>
+      <c r="I42" s="50"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A43:I43"/>
+  <mergeCells count="9">
     <mergeCell ref="A42:I42"/>
     <mergeCell ref="A41:I41"/>
     <mergeCell ref="A39:I39"/>
@@ -6905,13 +8425,13 @@
     <mergeCell ref="A37:I37"/>
     <mergeCell ref="A38:I38"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="21" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6925,27 +8445,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:3" s="42" customFormat="1" ht="35" customHeight="1">
-      <c r="B1" s="69" t="s">
-        <v>301</v>
-      </c>
-      <c r="C1" s="69"/>
+      <c r="B1" s="70" t="s">
+        <v>299</v>
+      </c>
+      <c r="C1" s="70"/>
     </row>
     <row r="2" spans="2:3" ht="50" customHeight="1">
-      <c r="B2" s="70" t="s">
-        <v>322</v>
-      </c>
-      <c r="C2" s="70"/>
+      <c r="B2" s="71" t="s">
+        <v>318</v>
+      </c>
+      <c r="C2" s="71"/>
     </row>
     <row r="4" spans="2:3" ht="15" customHeight="1">
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="45" t="s">
+      <c r="C4" s="44" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15" customHeight="1">
-      <c r="B5" s="46" t="s">
+      <c r="B5" s="45" t="s">
         <v>95</v>
       </c>
       <c r="C5" s="23" t="s">
@@ -6953,7 +8473,7 @@
       </c>
     </row>
     <row r="6" spans="2:3" ht="15" customHeight="1">
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="45" t="s">
         <v>97</v>
       </c>
       <c r="C6" s="23" t="s">
@@ -6961,7 +8481,7 @@
       </c>
     </row>
     <row r="7" spans="2:3" ht="15" customHeight="1">
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="45" t="s">
         <v>99</v>
       </c>
       <c r="C7" s="23" t="s">
@@ -6969,7 +8489,7 @@
       </c>
     </row>
     <row r="8" spans="2:3" ht="15" customHeight="1">
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="45" t="s">
         <v>101</v>
       </c>
       <c r="C8" s="23" t="s">
@@ -6977,7 +8497,7 @@
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="45" t="s">
         <v>102</v>
       </c>
       <c r="C9" s="23" t="s">
@@ -6985,7 +8505,7 @@
       </c>
     </row>
     <row r="10" spans="2:3" ht="15" customHeight="1">
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="45" t="s">
         <v>103</v>
       </c>
       <c r="C10" s="23" t="s">
@@ -6993,7 +8513,7 @@
       </c>
     </row>
     <row r="11" spans="2:3" ht="15" customHeight="1">
-      <c r="B11" s="46" t="s">
+      <c r="B11" s="45" t="s">
         <v>104</v>
       </c>
       <c r="C11" s="23" t="s">
@@ -7001,7 +8521,7 @@
       </c>
     </row>
     <row r="12" spans="2:3" ht="15" customHeight="1">
-      <c r="B12" s="46" t="s">
+      <c r="B12" s="45" t="s">
         <v>106</v>
       </c>
       <c r="C12" s="23" t="s">
@@ -7009,7 +8529,7 @@
       </c>
     </row>
     <row r="13" spans="2:3" ht="15" customHeight="1">
-      <c r="B13" s="46" t="s">
+      <c r="B13" s="45" t="s">
         <v>108</v>
       </c>
       <c r="C13" s="23" t="s">
@@ -7017,7 +8537,7 @@
       </c>
     </row>
     <row r="14" spans="2:3" ht="15" customHeight="1">
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="45" t="s">
         <v>110</v>
       </c>
       <c r="C14" s="23" t="s">
@@ -7025,7 +8545,7 @@
       </c>
     </row>
     <row r="15" spans="2:3" ht="15" customHeight="1">
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="45" t="s">
         <v>112</v>
       </c>
       <c r="C15" s="23" t="s">
@@ -7033,7 +8553,7 @@
       </c>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="45" t="s">
         <v>114</v>
       </c>
       <c r="C16" s="23" t="s">
@@ -7041,7 +8561,7 @@
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="46" t="s">
+      <c r="B17" s="45" t="s">
         <v>116</v>
       </c>
       <c r="C17" s="23" t="s">
@@ -7049,7 +8569,7 @@
       </c>
     </row>
     <row r="18" spans="2:3" ht="15" customHeight="1">
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="45" t="s">
         <v>118</v>
       </c>
       <c r="C18" s="23" t="s">
@@ -7057,7 +8577,7 @@
       </c>
     </row>
     <row r="19" spans="2:3" ht="15" customHeight="1">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="45" t="s">
         <v>120</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -7065,7 +8585,7 @@
       </c>
     </row>
     <row r="20" spans="2:3" ht="15" customHeight="1">
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="45" t="s">
         <v>122</v>
       </c>
       <c r="C20" s="23" t="s">
@@ -7073,7 +8593,7 @@
       </c>
     </row>
     <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="B21" s="46" t="s">
+      <c r="B21" s="45" t="s">
         <v>123</v>
       </c>
       <c r="C21" s="23" t="s">
@@ -7081,7 +8601,7 @@
       </c>
     </row>
     <row r="22" spans="2:3" ht="15" customHeight="1">
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="45" t="s">
         <v>124</v>
       </c>
       <c r="C22" s="23" t="s">
@@ -7089,7 +8609,7 @@
       </c>
     </row>
     <row r="23" spans="2:3" ht="15" customHeight="1">
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="45" t="s">
         <v>125</v>
       </c>
       <c r="C23" s="23" t="s">
@@ -7097,7 +8617,7 @@
       </c>
     </row>
     <row r="24" spans="2:3" ht="15" customHeight="1">
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="45" t="s">
         <v>126</v>
       </c>
       <c r="C24" s="23" t="s">
@@ -7105,7 +8625,7 @@
       </c>
     </row>
     <row r="25" spans="2:3" ht="15" customHeight="1">
-      <c r="B25" s="46" t="s">
+      <c r="B25" s="45" t="s">
         <v>128</v>
       </c>
       <c r="C25" s="23" t="s">
@@ -7113,7 +8633,7 @@
       </c>
     </row>
     <row r="26" spans="2:3" ht="15" customHeight="1">
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="45" t="s">
         <v>129</v>
       </c>
       <c r="C26" s="23" t="s">
@@ -7121,15 +8641,15 @@
       </c>
     </row>
     <row r="27" spans="2:3" ht="15" customHeight="1">
-      <c r="B27" s="46" t="s">
+      <c r="B27" s="45" t="s">
         <v>130</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="15" customHeight="1">
-      <c r="B28" s="46" t="s">
+      <c r="B28" s="45" t="s">
         <v>131</v>
       </c>
       <c r="C28" s="23" t="s">
@@ -7141,13 +8661,13 @@
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="86" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25CC5AF0-2FB9-4BAE-BF00-C21E9526F362}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7162,16 +8682,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
-      <c r="B1" s="73" t="s">
-        <v>402</v>
-      </c>
-      <c r="C1" s="73"/>
+      <c r="B1" s="74" t="s">
+        <v>397</v>
+      </c>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1">
-      <c r="B2" s="74" t="s">
-        <v>403</v>
-      </c>
-      <c r="C2" s="74"/>
+      <c r="B2" s="75" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2" s="75"/>
     </row>
     <row r="3" spans="1:4">
       <c r="B3" s="33"/>
@@ -7182,35 +8702,35 @@
         <v>166</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="19.5" customHeight="1">
       <c r="B5" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>405</v>
-      </c>
-      <c r="D5" s="72" t="s">
-        <v>342</v>
+        <v>281</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>400</v>
+      </c>
+      <c r="D5" s="76" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="19.5" customHeight="1">
       <c r="B6" s="34" t="s">
-        <v>284</v>
-      </c>
-      <c r="C6" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C6" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="72"/>
+      <c r="D6" s="76"/>
     </row>
     <row r="7" spans="1:4" ht="19.5" customHeight="1">
       <c r="B7" s="34" t="s">
         <v>168</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="19.5" customHeight="1">
@@ -7218,7 +8738,7 @@
         <v>170</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="19.5" customHeight="1">
@@ -7226,33 +8746,33 @@
         <v>172</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="B11" s="73" t="s">
-        <v>282</v>
-      </c>
-      <c r="C11" s="73"/>
+      <c r="B11" s="74" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" s="74"/>
     </row>
     <row r="12" spans="1:4" ht="120" customHeight="1">
-      <c r="B12" s="75" t="s">
-        <v>408</v>
-      </c>
-      <c r="C12" s="75"/>
+      <c r="B12" s="73" t="s">
+        <v>403</v>
+      </c>
+      <c r="C12" s="73"/>
     </row>
     <row r="14" spans="1:4" ht="24" customHeight="1">
-      <c r="B14" s="73" t="s">
-        <v>411</v>
-      </c>
-      <c r="C14" s="73"/>
+      <c r="B14" s="74" t="s">
+        <v>406</v>
+      </c>
+      <c r="C14" s="74"/>
     </row>
     <row r="15" spans="1:4" ht="120" customHeight="1">
-      <c r="A15" s="88"/>
-      <c r="B15" s="89" t="s">
-        <v>410</v>
-      </c>
-      <c r="C15" s="75"/>
+      <c r="A15" s="48"/>
+      <c r="B15" s="72" t="s">
+        <v>405</v>
+      </c>
+      <c r="C15" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -7264,18 +8784,18 @@
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B14:C14"/>
   </mergeCells>
-  <phoneticPr fontId="22" type="noConversion"/>
+  <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="56" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:D25"/>
+  <dimension ref="B1:D29"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7285,16 +8805,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="24" customHeight="1">
-      <c r="B1" s="73" t="s">
-        <v>304</v>
-      </c>
-      <c r="C1" s="73"/>
+      <c r="B1" s="74" t="s">
+        <v>302</v>
+      </c>
+      <c r="C1" s="74"/>
     </row>
     <row r="2" spans="2:4" ht="30" customHeight="1">
-      <c r="B2" s="74" t="s">
-        <v>259</v>
-      </c>
-      <c r="C2" s="74"/>
+      <c r="B2" s="75" t="s">
+        <v>409</v>
+      </c>
+      <c r="C2" s="75"/>
     </row>
     <row r="3" spans="2:4">
       <c r="B3" s="33"/>
@@ -7305,28 +8825,28 @@
         <v>166</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="19.5" customHeight="1">
       <c r="B5" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="C5" s="47" t="s">
-        <v>406</v>
-      </c>
-      <c r="D5" s="72" t="s">
-        <v>342</v>
+        <v>281</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>401</v>
+      </c>
+      <c r="D5" s="76" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="19.5" customHeight="1">
       <c r="B6" s="34" t="s">
-        <v>284</v>
-      </c>
-      <c r="C6" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C6" s="46" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="72"/>
+      <c r="D6" s="76"/>
     </row>
     <row r="7" spans="2:4" ht="19.5" customHeight="1">
       <c r="B7" s="34" t="s">
@@ -7353,22 +8873,22 @@
       </c>
     </row>
     <row r="11" spans="2:4" ht="24" customHeight="1">
-      <c r="B11" s="73" t="s">
-        <v>282</v>
-      </c>
-      <c r="C11" s="73"/>
-    </row>
-    <row r="12" spans="2:4" ht="400" customHeight="1">
-      <c r="B12" s="75" t="s">
-        <v>344</v>
-      </c>
-      <c r="C12" s="75"/>
+      <c r="B11" s="74" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" s="74"/>
+    </row>
+    <row r="12" spans="2:4" ht="300" customHeight="1">
+      <c r="B12" s="73" t="s">
+        <v>339</v>
+      </c>
+      <c r="C12" s="73"/>
     </row>
     <row r="14" spans="2:4" ht="24" customHeight="1">
-      <c r="B14" s="73" t="s">
-        <v>305</v>
-      </c>
-      <c r="C14" s="73"/>
+      <c r="B14" s="74" t="s">
+        <v>410</v>
+      </c>
+      <c r="C14" s="74"/>
     </row>
     <row r="15" spans="2:4" ht="15" customHeight="1">
       <c r="B15" s="35" t="s">
@@ -7458,22 +8978,43 @@
         <v>195</v>
       </c>
     </row>
+    <row r="27" spans="2:3" ht="24" customHeight="1">
+      <c r="B27" s="74" t="s">
+        <v>411</v>
+      </c>
+      <c r="C27" s="74"/>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" s="79">
+        <v>46204</v>
+      </c>
+      <c r="C28" s="80"/>
+    </row>
+    <row r="29" spans="2:3" ht="300" customHeight="1">
+      <c r="B29" s="77" t="s">
+        <v>412</v>
+      </c>
+      <c r="C29" s="78"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D5:D6"/>
+  <mergeCells count="9">
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D5:D6"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="55" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7487,25 +9028,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="35" customHeight="1">
-      <c r="B1" s="76" t="s">
+      <c r="B1" s="81" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="76"/>
-      <c r="D1" s="76"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
     </row>
     <row r="2" spans="2:4" ht="42" customHeight="1">
-      <c r="B2" s="77" t="s">
-        <v>312</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
+      <c r="B2" s="82" t="s">
+        <v>309</v>
+      </c>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
     </row>
     <row r="3" spans="2:4" ht="21.5" customHeight="1">
-      <c r="B3" s="78" t="s">
+      <c r="B3" s="83" t="s">
         <v>197</v>
       </c>
-      <c r="C3" s="78"/>
-      <c r="D3" s="78"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
     </row>
     <row r="4" spans="2:4" ht="35" customHeight="1">
       <c r="B4" s="43" t="s">
@@ -7523,10 +9064,10 @@
         <v>201</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="D5" s="25" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="2:4" ht="55.5" customHeight="1">
@@ -7534,7 +9075,7 @@
         <v>202</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>203</v>
@@ -7545,10 +9086,10 @@
         <v>204</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="2:4" ht="55.5" customHeight="1">
@@ -7556,10 +9097,10 @@
         <v>205</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="2:4">
@@ -7568,18 +9109,18 @@
       <c r="D9" s="27"/>
     </row>
     <row r="10" spans="2:4" ht="42" customHeight="1">
-      <c r="B10" s="77" t="s">
-        <v>270</v>
-      </c>
-      <c r="C10" s="77"/>
-      <c r="D10" s="77"/>
+      <c r="B10" s="82" t="s">
+        <v>268</v>
+      </c>
+      <c r="C10" s="82"/>
+      <c r="D10" s="82"/>
     </row>
     <row r="12" spans="2:4" ht="100" customHeight="1">
-      <c r="B12" s="79" t="s">
-        <v>314</v>
-      </c>
-      <c r="C12" s="80"/>
-      <c r="D12" s="80"/>
+      <c r="B12" s="84" t="s">
+        <v>413</v>
+      </c>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -7589,13 +9130,13 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="B12:D12"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="71" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -7612,42 +9153,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="35" customHeight="1">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="87" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="87"/>
+      <c r="E1" s="87"/>
+      <c r="F1" s="87"/>
+      <c r="G1" s="87"/>
     </row>
     <row r="2" spans="1:7" ht="42" customHeight="1">
-      <c r="A2" s="83" t="s">
-        <v>306</v>
-      </c>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
+      <c r="A2" s="88" t="s">
+        <v>303</v>
+      </c>
+      <c r="B2" s="88"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="88"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="88"/>
+      <c r="G2" s="88"/>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1">
       <c r="A3" s="28" t="s">
         <v>198</v>
       </c>
       <c r="B3" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="C3" s="28" t="s">
+        <v>271</v>
+      </c>
+      <c r="D3" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="E3" s="28" t="s">
         <v>273</v>
-      </c>
-      <c r="D3" s="28" t="s">
-        <v>274</v>
-      </c>
-      <c r="E3" s="28" t="s">
-        <v>275</v>
       </c>
       <c r="F3" s="28" t="s">
         <v>207</v>
@@ -7746,7 +9287,7 @@
         <v>184</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C9" s="32" t="s">
         <v>15</v>
@@ -7797,7 +9338,7 @@
         <v>190</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C12" s="30" t="s">
         <v>27</v>
@@ -7950,7 +9491,7 @@
         <v>216</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C21" s="32" t="s">
         <v>42</v>
@@ -8123,7 +9664,7 @@
         <v>164</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D31" s="31"/>
       <c r="E31" s="31" t="s">
@@ -8184,15 +9725,15 @@
       <c r="G34" s="29"/>
     </row>
     <row r="36" spans="1:7" ht="43.5" customHeight="1">
-      <c r="A36" s="81" t="s">
-        <v>281</v>
-      </c>
-      <c r="B36" s="81"/>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
+      <c r="A36" s="86" t="s">
+        <v>279</v>
+      </c>
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="86"/>
+      <c r="E36" s="86"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8200,178 +9741,8 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
+  <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="67" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17"/>
-  <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="35.58203125" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="62" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" ht="30" customHeight="1">
-      <c r="A1" s="71" t="s">
-        <v>302</v>
-      </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-    </row>
-    <row r="2" spans="1:4" ht="27.75" customHeight="1">
-      <c r="A2" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="35" customHeight="1">
-      <c r="A3" s="3">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="35" customHeight="1">
-      <c r="A4" s="3">
-        <v>2</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="20" customHeight="1">
-      <c r="A5" s="3">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="20" customHeight="1">
-      <c r="A6" s="3">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="20" customHeight="1">
-      <c r="A7" s="3">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="20" customHeight="1">
-      <c r="A8" s="3">
-        <v>6</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="20" customHeight="1">
-      <c r="A9" s="3">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="20" customHeight="1">
-      <c r="A10" s="3">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="150" customHeight="1">
-      <c r="A11" s="3">
-        <v>9</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
-  </mergeCells>
-  <phoneticPr fontId="17" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="66" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/public/files/copyright-schedule-june-v5.xlsx
+++ b/public/files/copyright-schedule-june-v5.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\info\amy\public\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6ADA9D0-D319-4E3B-AE9F-BE73FED89926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8271D2B7-9B8E-42DE-A411-5F4CEFD36BCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AI매칭_프롬프트" sheetId="1" r:id="rId1"/>
+    <sheet name="프롬프트" sheetId="1" r:id="rId1"/>
     <sheet name="데드라인순" sheetId="6" r:id="rId2"/>
     <sheet name="7월_업무마스터" sheetId="12" r:id="rId3"/>
     <sheet name="6월_업무마스터" sheetId="2" r:id="rId4"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1074" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="421">
   <si>
     <t>구분</t>
   </si>
@@ -1172,101 +1172,7 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>※ Ai 매칭 활용 시 아래 프롬프트를 (gpt 5.4) 와 함께 사용. (누끼 동일 이미지 매칭)</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
     <t>※ 목표수량=트렐로 최종 기준 · 데드라인=전처리스케줄 6월 값 · 담당 브랜드 매월 변동 가능 · ⚠확인필요 ★이사님/담당자 확인 ✅6월 완료표기</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Cosmetic </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>저작권</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>탐지용</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>프롬프트</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (GPT 5.4 </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>사용</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="21" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -3237,10 +3143,6 @@
     <phoneticPr fontId="16" type="noConversion"/>
   </si>
   <si>
-    <t>※ Schedule Ai 활용 시 위 프롬프트를 (gpt 5.4 mini) 와 함께 사용. (누끼 동일 이미지 매칭)</t>
-    <phoneticPr fontId="16" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">   · 공식몰</t>
     </r>
@@ -4048,12 +3950,191 @@
     </r>
     <phoneticPr fontId="21" type="noConversion"/>
   </si>
+  <si>
+    <t>다음 상품/게시글이 PXG 가품 탐지 대상에서 제외할 “골프채/골프클럽 관련 데이터”인지 판별해 주세요.
+목적은 가품 탐지 대상 데이터 중에서 이번 작업 범위에서 제외하기로 한 골프채 데이터를 빠르게 선별하는 것입니다.  
+단순히 PXG 브랜드가 보이는지만 보지 말고, 제목/본문/해시태그/이미지를 종합하여 이 게시글의 중심 상품이 골프채 또는 골프클럽인지 판단해 주세요.
+[입력 정보]
+- 제목:
+- 본문/설명:
+- 해시태그:
+- 이미지:
+[판별 기준]
+1. “골프채 제외 대상”으로 분류할 수 있는 경우
+다음과 같은 단어가 제목, 본문, 해시태그에 포함되어 있고, 중심 상품이 골프채/골프클럽으로 보이면 제외 대상으로 분류해 주세요.
+[주요 골프채 키워드]
+- 골프채
+- 골프클럽
+- 클럽
+- 드라이버
+- driver
+- 1W
+- 1번 우드
+- 페어웨이 우드
+- 페어웨이우드
+- fairway wood
+- 우드
+- wood
+- FW
+- 3W
+- 5W
+- 유틸리티
+- 유틸
+- 하이브리드
+- hybrid
+- utility
+- UT
+- 아이언
+- iron
+- 아이언세트
+- iron set
+- 세트 아이언
+- 웨지
+- 웻지
+- wedge
+- AW
+- GW
+- SW
+- LW
+- 퍼터
+- putter
+- 풀세트
+- full set
+- 클럽세트
+- club set
+[골프채 관련 부품/구성품 키워드]
+아래 단어가 포함된 경우에는 골프채 관련 데이터일 가능성이 있으므로, 중심 상품이 실제 골프채 또는 클럽 구성품인지 확인해 주세요.
+- 샤프트
+- shaft
+- 그립
+- grip
+- 헤드
+- club head
+- 헤드 단품
+- 렌치
+- 조립 클럽
+- 피팅 클럽
+단, 샤프트/그립/헤드만 판매하는 경우에는 “골프채 관련 제외 후보”로 볼 수 있지만, 완제품 골프채보다 확신도가 낮을 수 있으므로 근거를 명확히 적어 주세요.
+2. “골프채 제외 대상 아님”으로 분류할 수 있는 경우
+아래 상품들은 PXG 관련 상품일 수 있어도, 중심 상품이 골프채가 아니므로 골프채 제외 대상으로 분류하지 마세요.
+[골프채가 아닌 상품 예시]
+- 의류
+- 모자
+- 골프웨어
+- 티셔츠
+- 카라티
+- 바지
+- 스커트
+- 조끼
+- 점퍼
+- 장갑
+- 골프화
+- 양말
+- 벨트
+- 가방
+- 캐디백
+- 보스턴백
+- 파우치
+- 볼주머니
+- 골프공
+- 볼마커
+- 티
+- 타월
+- 우산
+- 마커
+- 액세서리
+- 스티커
+- 로고 패치
+3. 주의해야 할 예외
+제목에 “드라이버”, “우드”, “퍼터” 등의 단어가 포함되어 있어도, 실제 중심 상품이 골프채가 아닌 경우에는 제외 대상으로 분류하지 마세요.
+예시:
+- “PXG 드라이버 헤드커버” → 골프채가 아니라 헤드커버이므로 제외 대상 아님
+- “PXG 퍼터 커버” → 퍼터가 아니라 커버이므로 제외 대상 아님
+- “PXG 아이언 커버 세트” → 아이언이 아니라 커버이므로 제외 대상 아님
+- “PXG 드라이버 렌치” → 골프채 자체가 아니므로 수동 확인 또는 제외 대상 아님
+- “PXG 골프백 with driver” → 중심 상품이 골프백이면 제외 대상 아님
+4. 이미지 판단 기준
+이미지가 제공되는 경우, 다음 요소를 확인해 주세요.
+[골프채로 볼 수 있는 이미지 특징]
+- 긴 샤프트가 있는 클럽 형태
+- 드라이버/우드처럼 큰 헤드가 달린 클럽
+- 아이언 헤드가 여러 개 배열된 세트
+- 웨지/퍼터 형태의 금속 헤드
+- 클럽 여러 개가 세트로 진열된 이미지
+- 클럽 단품 또는 클럽 헤드가 중심에 놓인 이미지
+[골프채가 아닌 이미지 특징]
+- 의류 착용컷
+- 모자, 가방, 장갑, 신발 중심 이미지
+- 헤드커버, 파우치, 볼마커 등 액세서리 중심 이미지
+- 클럽이 배경에 일부 보이지만 판매 대상은 의류/가방/액세서리인 경우
+5. 판정 원칙
+- 제목에 골프채 키워드가 있고 이미지도 골프채로 보이면 “골프채_제외대상”으로 분류하세요.
+- 제목에 골프채 키워드가 있어도 “커버”, “케이스”, “가방”, “파우치”, “액세서리”와 함께 쓰이면 골프채 자체인지 다시 확인하세요.
+- 중심 상품이 명확하지 않으면 무리하게 제외하지 말고 “수동확인필요”로 분류하세요.
+- 단어 하나만 보고 판정하지 말고, 제목의 전체 의미와 이미지의 중심 상품을 함께 보세요.
+- PXG 브랜드 여부보다 “상품 종류가 골프채인지”가 더 중요합니다.
+[출력 형식]
+아래 형식으로만 답변해 주세요.
+판정: 골프채_제외대상 / 비골프채_검수유지 / 수동확인필요
+확신도: 높음 / 중간 / 낮음
+매칭 키워드: 
+근거:
+권장 처리:</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>[IG-PXG] 데이터 분류</t>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
+  <si>
+    <t>※ Schedule Ai (Ai 매칭) 활용 시 아래 프롬프트를 (gpt 5.4 mini) 와 함께 사용. (누끼 동일 이미지 매칭)</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <t>※ Schedule Ai (Ai 매칭) 활용 시 아래 프롬프트를 (gpt 5.4 mini) 와 함께 사용.</t>
+    <phoneticPr fontId="16" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>(Cosmetics) 저작권</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>탐지</t>
+    </r>
+    <phoneticPr fontId="21" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="42">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4337,6 +4418,14 @@
       <name val="Calibri"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Noto Sans CJK SC"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="20">
     <fill>
@@ -4607,12 +4696,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4840,6 +4923,12 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5109,7 +5198,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="8.5" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5117,10 +5206,10 @@
     <col min="9" max="9" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="35" customHeight="1">
+    <row r="1" spans="1:9" ht="30" customHeight="1">
       <c r="A1" s="5"/>
-      <c r="B1" s="9" t="s">
-        <v>261</v>
+      <c r="B1" s="89" t="s">
+        <v>420</v>
       </c>
       <c r="C1" s="7"/>
       <c r="D1" s="5"/>
@@ -5132,8 +5221,8 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="5"/>
-      <c r="B2" s="8" t="s">
-        <v>259</v>
+      <c r="B2" s="88" t="s">
+        <v>418</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -5154,20 +5243,34 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9" ht="400">
+    <row r="4" spans="1:9" ht="400" customHeight="1">
       <c r="B4" s="6" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="B6" s="8" t="s">
-        <v>407</v>
+        <v>276</v>
+      </c>
+      <c r="D4" s="46"/>
+    </row>
+    <row r="6" spans="1:9" ht="30" customHeight="1">
+      <c r="B6" s="41" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="B7" s="88" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8" s="5"/>
+    </row>
+    <row r="9" spans="1:9" ht="400" customHeight="1">
+      <c r="B9" s="6" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="16" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="82" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="75" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -5186,12 +5289,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="30" customHeight="1">
-      <c r="A1" s="89" t="s">
-        <v>300</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
+      <c r="A1" s="87" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
     </row>
     <row r="2" spans="1:4" ht="27.75" customHeight="1">
       <c r="A2" s="2" t="s">
@@ -5218,7 +5321,7 @@
         <v>146</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="35" customHeight="1">
@@ -5232,7 +5335,7 @@
         <v>148</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20" customHeight="1">
@@ -5254,7 +5357,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>152</v>
@@ -5274,7 +5377,7 @@
         <v>148</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="20" customHeight="1">
@@ -5316,7 +5419,7 @@
         <v>162</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="150" customHeight="1">
@@ -5324,11 +5427,11 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C11" s="3"/>
       <c r="D11" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>
@@ -5356,13 +5459,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="89" t="s">
-        <v>296</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
-      <c r="E1" s="61"/>
+      <c r="A1" s="87" t="s">
+        <v>294</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
     </row>
     <row r="2" spans="1:5" ht="27.75" customHeight="1">
       <c r="A2" s="1" t="s">
@@ -5375,7 +5478,7 @@
         <v>134</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
@@ -5386,12 +5489,12 @@
         <v>29</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="D3" s="40" t="s">
+        <v>289</v>
+      </c>
+      <c r="D3" s="38" t="s">
         <v>135</v>
       </c>
       <c r="E3" s="3" t="s">
@@ -5406,9 +5509,9 @@
         <v>248</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D4" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="D4" s="38" t="s">
         <v>135</v>
       </c>
       <c r="E4" s="3" t="s">
@@ -5423,9 +5526,9 @@
         <v>248</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D5" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="D5" s="38" t="s">
         <v>135</v>
       </c>
       <c r="E5" s="3" t="s">
@@ -5440,9 +5543,9 @@
         <v>248</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D6" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="D6" s="38" t="s">
         <v>135</v>
       </c>
       <c r="E6" s="3" t="s">
@@ -5457,9 +5560,9 @@
         <v>248</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="D7" s="40" t="s">
+        <v>290</v>
+      </c>
+      <c r="D7" s="38" t="s">
         <v>135</v>
       </c>
       <c r="E7" s="3" t="s">
@@ -5471,12 +5574,12 @@
         <v>21</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="D8" s="41" t="s">
+        <v>281</v>
+      </c>
+      <c r="D8" s="39" t="s">
         <v>138</v>
       </c>
       <c r="E8" s="3" t="s">
@@ -5488,16 +5591,16 @@
         <v>140</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="D9" s="40" t="s">
+        <v>292</v>
+      </c>
+      <c r="D9" s="38" t="s">
         <v>135</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -5525,16 +5628,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1">
-      <c r="A1" s="60" t="s">
-        <v>301</v>
-      </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="61"/>
+      <c r="A1" s="58" t="s">
+        <v>299</v>
+      </c>
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="59"/>
     </row>
     <row r="2" spans="1:5" ht="27.75" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
@@ -5546,7 +5649,7 @@
         <v>163</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="17" customHeight="1">
@@ -5563,7 +5666,7 @@
         <v>248</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="17" customHeight="1">
@@ -5580,7 +5683,7 @@
         <v>248</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="17" customHeight="1">
@@ -5597,7 +5700,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="17" customHeight="1">
@@ -5611,10 +5714,10 @@
         <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="17" customHeight="1">
@@ -5622,21 +5725,21 @@
         <v>244</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>239</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="17" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>41</v>
@@ -5653,7 +5756,7 @@
     </row>
     <row r="9" spans="1:5" ht="17" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>46</v>
@@ -5670,7 +5773,7 @@
     </row>
     <row r="10" spans="1:5" ht="17" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>48</v>
@@ -5704,7 +5807,7 @@
     </row>
     <row r="12" spans="1:5" ht="17" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>164</v>
@@ -5730,605 +5833,605 @@
         <v>77</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="17" customHeight="1">
+      <c r="A14" s="37" t="s">
+        <v>246</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>355</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17" customHeight="1">
+      <c r="A15" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="17" customHeight="1">
+      <c r="A16" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="17" customHeight="1">
+      <c r="A17" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="17" customHeight="1">
+      <c r="A18" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="17" customHeight="1">
+      <c r="A19" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="17" customHeight="1">
+      <c r="A20" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="17" customHeight="1">
+      <c r="A21" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="17" customHeight="1">
+      <c r="A22" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="17" customHeight="1">
+      <c r="A23" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="17" customHeight="1">
+      <c r="A24" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="17" customHeight="1">
+      <c r="A25" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="17" customHeight="1">
+      <c r="A26" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="D26" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="35" customHeight="1">
+      <c r="A27" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="17" customHeight="1">
+      <c r="A28" s="60"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="62"/>
+    </row>
+    <row r="29" spans="1:5" ht="17" customHeight="1">
+      <c r="A29" s="21" t="s">
+        <v>390</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="17" customHeight="1">
+      <c r="A30" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D30" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="35" customHeight="1">
+      <c r="A31" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="E31" s="21" t="s">
         <v>394</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="17" customHeight="1">
-      <c r="A14" s="39" t="s">
-        <v>246</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="39" t="s">
+    </row>
+    <row r="32" spans="1:5" ht="50" customHeight="1">
+      <c r="A32" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D32" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="17" customHeight="1">
+      <c r="A33" s="60"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="62"/>
+    </row>
+    <row r="34" spans="1:5" ht="17" customHeight="1">
+      <c r="A34" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D34" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="17" customHeight="1">
+      <c r="A35" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="17" customHeight="1">
+      <c r="A36" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D36" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="17" customHeight="1">
+      <c r="A37" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="B37" s="21" t="s">
         <v>357</v>
       </c>
-      <c r="E14" s="39" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="17" customHeight="1">
-      <c r="A15" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B15" s="23" t="s">
+      <c r="C37" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="17" customHeight="1">
+      <c r="A38" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="17" customHeight="1">
-      <c r="A16" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B16" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="23" t="s">
-        <v>248</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="17" customHeight="1">
-      <c r="A17" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B17" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D17" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="23" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="17" customHeight="1">
-      <c r="A18" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="17" customHeight="1">
-      <c r="A19" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B19" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="23" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="23" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="17" customHeight="1">
-      <c r="A20" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B20" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="23" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="17" customHeight="1">
-      <c r="A21" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D21" s="23" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="23" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="17" customHeight="1">
-      <c r="A22" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="17" customHeight="1">
-      <c r="A23" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="17" customHeight="1">
-      <c r="A24" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="B24" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="D24" s="23" t="s">
-        <v>60</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="17" customHeight="1">
-      <c r="A25" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="B25" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D25" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="E25" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="17" customHeight="1">
-      <c r="A26" s="23" t="s">
-        <v>343</v>
-      </c>
-      <c r="B26" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" ht="35" customHeight="1">
-      <c r="A27" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="C27" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="23" t="s">
-        <v>355</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="17" customHeight="1">
-      <c r="A28" s="62"/>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="64"/>
-    </row>
-    <row r="29" spans="1:5" ht="17" customHeight="1">
-      <c r="A29" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="B29" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="C29" s="23" t="s">
+      <c r="B38" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="17" customHeight="1">
-      <c r="A30" s="23" t="s">
-        <v>365</v>
-      </c>
-      <c r="B30" s="23" t="s">
+      <c r="D38" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="17" customHeight="1">
+      <c r="A39" s="60"/>
+      <c r="B39" s="61"/>
+      <c r="C39" s="61"/>
+      <c r="D39" s="61"/>
+      <c r="E39" s="62"/>
+    </row>
+    <row r="40" spans="1:5" ht="30" customHeight="1">
+      <c r="A40" s="67" t="s">
+        <v>324</v>
+      </c>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="66" t="s">
+        <v>338</v>
+      </c>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
+      <c r="D41" s="66"/>
+      <c r="E41" s="66"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="57" t="s">
+        <v>322</v>
+      </c>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="57" t="s">
+        <v>321</v>
+      </c>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="57" t="s">
+        <v>375</v>
+      </c>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="57" t="s">
+        <v>323</v>
+      </c>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="63" t="s">
+        <v>325</v>
+      </c>
+      <c r="B46" s="64"/>
+      <c r="C46" s="64"/>
+      <c r="D46" s="64"/>
+      <c r="E46" s="65"/>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="63" t="s">
+        <v>326</v>
+      </c>
+      <c r="B47" s="64"/>
+      <c r="C47" s="64"/>
+      <c r="D47" s="64"/>
+      <c r="E47" s="65"/>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="63" t="s">
+        <v>328</v>
+      </c>
+      <c r="B48" s="64"/>
+      <c r="C48" s="64"/>
+      <c r="D48" s="64"/>
+      <c r="E48" s="65"/>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="63" t="s">
+        <v>329</v>
+      </c>
+      <c r="B49" s="64"/>
+      <c r="C49" s="64"/>
+      <c r="D49" s="64"/>
+      <c r="E49" s="65"/>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="63" t="s">
+        <v>330</v>
+      </c>
+      <c r="B50" s="64"/>
+      <c r="C50" s="64"/>
+      <c r="D50" s="64"/>
+      <c r="E50" s="65"/>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="63" t="s">
+        <v>327</v>
+      </c>
+      <c r="B51" s="64"/>
+      <c r="C51" s="64"/>
+      <c r="D51" s="64"/>
+      <c r="E51" s="65"/>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="57" t="s">
+        <v>373</v>
+      </c>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="57" t="s">
         <v>374</v>
       </c>
-      <c r="C30" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="35" customHeight="1">
-      <c r="A31" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="B31" s="23" t="s">
-        <v>358</v>
-      </c>
-      <c r="C31" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>367</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="50" customHeight="1">
-      <c r="A32" s="23" t="s">
-        <v>364</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>373</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="17" customHeight="1">
-      <c r="A33" s="62"/>
-      <c r="B33" s="63"/>
-      <c r="C33" s="63"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="64"/>
-    </row>
-    <row r="34" spans="1:5" ht="17" customHeight="1">
-      <c r="A34" s="23" t="s">
-        <v>363</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>362</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="17" customHeight="1">
-      <c r="A35" s="23" t="s">
-        <v>363</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>361</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D35" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="E35" s="23" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="17" customHeight="1">
-      <c r="A36" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>360</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="17" customHeight="1">
-      <c r="A37" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="B37" s="23" t="s">
-        <v>359</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D37" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="E37" s="23" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" ht="17" customHeight="1">
-      <c r="A38" s="23" t="s">
-        <v>371</v>
-      </c>
-      <c r="B38" s="23" t="s">
-        <v>372</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>366</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" ht="17" customHeight="1">
-      <c r="A39" s="62"/>
-      <c r="B39" s="63"/>
-      <c r="C39" s="63"/>
-      <c r="D39" s="63"/>
-      <c r="E39" s="64"/>
-    </row>
-    <row r="40" spans="1:5" ht="30" customHeight="1">
-      <c r="A40" s="69" t="s">
-        <v>326</v>
-      </c>
-      <c r="B40" s="69"/>
-      <c r="C40" s="69"/>
-      <c r="D40" s="69"/>
-      <c r="E40" s="69"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="68" t="s">
-        <v>340</v>
-      </c>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="59" t="s">
-        <v>324</v>
-      </c>
-      <c r="B42" s="59"/>
-      <c r="C42" s="59"/>
-      <c r="D42" s="59"/>
-      <c r="E42" s="59"/>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="59" t="s">
-        <v>323</v>
-      </c>
-      <c r="B43" s="59"/>
-      <c r="C43" s="59"/>
-      <c r="D43" s="59"/>
-      <c r="E43" s="59"/>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="59" t="s">
-        <v>377</v>
-      </c>
-      <c r="B44" s="59"/>
-      <c r="C44" s="59"/>
-      <c r="D44" s="59"/>
-      <c r="E44" s="59"/>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="59" t="s">
-        <v>325</v>
-      </c>
-      <c r="B45" s="59"/>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="65" t="s">
-        <v>327</v>
-      </c>
-      <c r="B46" s="66"/>
-      <c r="C46" s="66"/>
-      <c r="D46" s="66"/>
-      <c r="E46" s="67"/>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="65" t="s">
-        <v>328</v>
-      </c>
-      <c r="B47" s="66"/>
-      <c r="C47" s="66"/>
-      <c r="D47" s="66"/>
-      <c r="E47" s="67"/>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="65" t="s">
-        <v>330</v>
-      </c>
-      <c r="B48" s="66"/>
-      <c r="C48" s="66"/>
-      <c r="D48" s="66"/>
-      <c r="E48" s="67"/>
-    </row>
-    <row r="49" spans="1:5">
-      <c r="A49" s="65" t="s">
-        <v>331</v>
-      </c>
-      <c r="B49" s="66"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="66"/>
-      <c r="E49" s="67"/>
-    </row>
-    <row r="50" spans="1:5">
-      <c r="A50" s="65" t="s">
-        <v>332</v>
-      </c>
-      <c r="B50" s="66"/>
-      <c r="C50" s="66"/>
-      <c r="D50" s="66"/>
-      <c r="E50" s="67"/>
-    </row>
-    <row r="51" spans="1:5">
-      <c r="A51" s="65" t="s">
-        <v>329</v>
-      </c>
-      <c r="B51" s="66"/>
-      <c r="C51" s="66"/>
-      <c r="D51" s="66"/>
-      <c r="E51" s="67"/>
-    </row>
-    <row r="52" spans="1:5">
-      <c r="A52" s="59" t="s">
-        <v>375</v>
-      </c>
-      <c r="B52" s="59"/>
-      <c r="C52" s="59"/>
-      <c r="D52" s="59"/>
-      <c r="E52" s="59"/>
-    </row>
-    <row r="53" spans="1:5">
-      <c r="A53" s="59" t="s">
-        <v>376</v>
-      </c>
-      <c r="B53" s="59"/>
-      <c r="C53" s="59"/>
-      <c r="D53" s="59"/>
-      <c r="E53" s="59"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
     </row>
     <row r="54" spans="1:5">
-      <c r="A54" s="58"/>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
+      <c r="A54" s="56"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="56"/>
+      <c r="D54" s="56"/>
+      <c r="E54" s="56"/>
     </row>
     <row r="55" spans="1:5">
-      <c r="A55" s="58"/>
-      <c r="B55" s="58"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="58"/>
+      <c r="A55" s="56"/>
+      <c r="B55" s="56"/>
+      <c r="C55" s="56"/>
+      <c r="D55" s="56"/>
+      <c r="E55" s="56"/>
     </row>
     <row r="56" spans="1:5">
-      <c r="A56" s="58"/>
-      <c r="B56" s="58"/>
-      <c r="C56" s="58"/>
-      <c r="D56" s="58"/>
-      <c r="E56" s="58"/>
+      <c r="A56" s="56"/>
+      <c r="B56" s="56"/>
+      <c r="C56" s="56"/>
+      <c r="D56" s="56"/>
+      <c r="E56" s="56"/>
     </row>
     <row r="57" spans="1:5">
-      <c r="A57" s="58"/>
-      <c r="B57" s="58"/>
-      <c r="C57" s="58"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="58"/>
+      <c r="A57" s="56"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="56"/>
+      <c r="D57" s="56"/>
+      <c r="E57" s="56"/>
     </row>
     <row r="58" spans="1:5">
-      <c r="A58" s="58"/>
-      <c r="B58" s="58"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="58"/>
+      <c r="A58" s="56"/>
+      <c r="B58" s="56"/>
+      <c r="C58" s="56"/>
+      <c r="D58" s="56"/>
+      <c r="E58" s="56"/>
     </row>
     <row r="59" spans="1:5">
-      <c r="A59" s="58"/>
-      <c r="B59" s="58"/>
-      <c r="C59" s="58"/>
-      <c r="D59" s="58"/>
-      <c r="E59" s="58"/>
+      <c r="A59" s="56"/>
+      <c r="B59" s="56"/>
+      <c r="C59" s="56"/>
+      <c r="D59" s="56"/>
+      <c r="E59" s="56"/>
     </row>
     <row r="60" spans="1:5">
-      <c r="A60" s="58"/>
-      <c r="B60" s="58"/>
-      <c r="C60" s="58"/>
-      <c r="D60" s="58"/>
-      <c r="E60" s="58"/>
+      <c r="A60" s="56"/>
+      <c r="B60" s="56"/>
+      <c r="C60" s="56"/>
+      <c r="D60" s="56"/>
+      <c r="E60" s="56"/>
     </row>
     <row r="61" spans="1:5">
-      <c r="A61" s="58"/>
-      <c r="B61" s="58"/>
-      <c r="C61" s="58"/>
-      <c r="D61" s="58"/>
-      <c r="E61" s="58"/>
+      <c r="A61" s="56"/>
+      <c r="B61" s="56"/>
+      <c r="C61" s="56"/>
+      <c r="D61" s="56"/>
+      <c r="E61" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -6382,1009 +6485,1009 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="50" customHeight="1">
-      <c r="A1" s="53" t="s">
-        <v>417</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
+      <c r="A1" s="51" t="s">
+        <v>414</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A2" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
+      <c r="A2" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
     </row>
     <row r="3" spans="1:9" ht="50" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="50" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="50" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="50" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="50" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="50" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="100" customHeight="1">
+      <c r="A10" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="50" customHeight="1">
-      <c r="A4" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="G10" s="11"/>
+      <c r="H10" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50" customHeight="1">
+      <c r="A11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50" customHeight="1">
+      <c r="A12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" ht="100" customHeight="1">
+      <c r="A13" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" ht="100" customHeight="1">
+      <c r="A14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I4" s="13" t="s">
+      <c r="G14" s="11"/>
+      <c r="H14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:9" ht="100" customHeight="1">
+      <c r="A15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:9" ht="100" customHeight="1">
+      <c r="A16" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" ht="100" customHeight="1">
+      <c r="A17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="100" customHeight="1">
+      <c r="A18" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="100" customHeight="1">
+      <c r="A19" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="100" customHeight="1">
+      <c r="A20" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="100" customHeight="1">
+      <c r="A21" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50" customHeight="1">
-      <c r="A5" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="50" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="50" customHeight="1">
-      <c r="A7" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="50" customHeight="1">
-      <c r="A8" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="13" t="s">
+    <row r="22" spans="1:9" ht="100" customHeight="1">
+      <c r="A22" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="170" customHeight="1">
+      <c r="A23" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="170" customHeight="1">
+      <c r="A24" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="50" customHeight="1">
+      <c r="A25" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="50" customHeight="1">
+      <c r="A26" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="50" customHeight="1">
+      <c r="A27" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="11"/>
+      <c r="H27" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="180" customHeight="1">
+      <c r="A28" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="180" customHeight="1">
+      <c r="A29" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="180" customHeight="1">
+      <c r="A30" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="100" customHeight="1">
+      <c r="A31" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="I31" s="45" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="100" customHeight="1">
+      <c r="A32" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="I32" s="45" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="100" customHeight="1">
+      <c r="A33" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="50" customHeight="1">
-      <c r="A9" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="100" customHeight="1">
-      <c r="A10" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="50" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="13" t="s">
+      <c r="F33" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="I33" s="20"/>
+    </row>
+    <row r="34" spans="1:9" ht="100" customHeight="1">
+      <c r="A34" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="50" customHeight="1">
-      <c r="A12" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="13"/>
-    </row>
-    <row r="13" spans="1:9" ht="100" customHeight="1">
-      <c r="A13" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="13"/>
-    </row>
-    <row r="14" spans="1:9" ht="100" customHeight="1">
-      <c r="A14" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="13"/>
-    </row>
-    <row r="15" spans="1:9" ht="100" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="16" spans="1:9" ht="100" customHeight="1">
-      <c r="A16" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="I16" s="13"/>
-    </row>
-    <row r="17" spans="1:9" ht="100" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="100" customHeight="1">
-      <c r="A18" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="100" customHeight="1">
-      <c r="A19" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="100" customHeight="1">
-      <c r="A20" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="100" customHeight="1">
-      <c r="A21" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="100" customHeight="1">
-      <c r="A22" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="170" customHeight="1">
-      <c r="A23" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="170" customHeight="1">
-      <c r="A24" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="13"/>
-      <c r="H24" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="50" customHeight="1">
-      <c r="A25" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G25" s="13"/>
-      <c r="H25" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="50" customHeight="1">
-      <c r="A26" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="50" customHeight="1">
-      <c r="A27" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="180" customHeight="1">
-      <c r="A28" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="I28" s="21" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="180" customHeight="1">
-      <c r="A29" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="180" customHeight="1">
-      <c r="A30" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>415</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="100" customHeight="1">
-      <c r="A31" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="I31" s="47" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="100" customHeight="1">
-      <c r="A32" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>416</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="I32" s="47" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="100" customHeight="1">
-      <c r="A33" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="I33" s="22"/>
-    </row>
-    <row r="34" spans="1:9" ht="100" customHeight="1">
-      <c r="A34" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="I34" s="20" t="s">
         <v>335</v>
-      </c>
-      <c r="H34" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="I34" s="22" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="19.5" customHeight="1"/>
     <row r="36" spans="1:9" ht="35" customHeight="1">
-      <c r="A36" s="56" t="s">
-        <v>262</v>
-      </c>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
+      <c r="A36" s="54" t="s">
+        <v>260</v>
+      </c>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
     <row r="37" spans="1:9" ht="30" customHeight="1">
-      <c r="A37" s="55" t="s">
+      <c r="A37" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="55"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="55"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
     </row>
     <row r="39" spans="1:9" ht="50" customHeight="1">
-      <c r="A39" s="52" t="s">
-        <v>408</v>
-      </c>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52"/>
+      <c r="A39" s="50" t="s">
+        <v>405</v>
+      </c>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="50"/>
     </row>
     <row r="40" spans="1:9" ht="30" customHeight="1">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="55"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
     </row>
     <row r="41" spans="1:9" ht="75" customHeight="1">
-      <c r="A41" s="51" t="s">
-        <v>305</v>
-      </c>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
+      <c r="A41" s="49" t="s">
+        <v>303</v>
+      </c>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
     </row>
     <row r="42" spans="1:9" ht="160" customHeight="1">
-      <c r="A42" s="51" t="s">
-        <v>414</v>
-      </c>
-      <c r="B42" s="51"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="51"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-    </row>
-    <row r="43" spans="1:9">
+      <c r="A42" s="49" t="s">
+        <v>411</v>
+      </c>
+      <c r="B42" s="49"/>
+      <c r="C42" s="49"/>
+      <c r="D42" s="49"/>
+      <c r="E42" s="49"/>
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+    </row>
+    <row r="43" spans="1:9" ht="17" customHeight="1">
       <c r="A43" s="49"/>
-      <c r="B43" s="50"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="50"/>
-      <c r="I43" s="50"/>
+      <c r="B43" s="49"/>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -7422,996 +7525,996 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="50" customHeight="1">
-      <c r="A1" s="53" t="s">
-        <v>418</v>
-      </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
+      <c r="A1" s="51" t="s">
+        <v>415</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
     </row>
     <row r="2" spans="1:9" ht="31.5" customHeight="1">
-      <c r="A2" s="54" t="s">
-        <v>260</v>
-      </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
+      <c r="A2" s="52" t="s">
+        <v>259</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
     </row>
     <row r="3" spans="1:9" ht="50" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="9" t="s">
         <v>258</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="50" customHeight="1">
+      <c r="A4" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="50" customHeight="1">
+      <c r="A5" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="50" customHeight="1">
+      <c r="A6" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="50" customHeight="1">
+      <c r="A7" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="50" customHeight="1">
+      <c r="A8" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="50" customHeight="1">
+      <c r="A9" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="100" customHeight="1">
+      <c r="A10" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="11" t="s">
         <v>379</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="50" customHeight="1">
-      <c r="A4" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="13" t="s">
+      <c r="G10" s="11"/>
+      <c r="H10" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="50" customHeight="1">
+      <c r="A11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="50" customHeight="1">
+      <c r="A12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" ht="100" customHeight="1">
+      <c r="A13" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="1:9" ht="100" customHeight="1">
+      <c r="A14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F14" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="D4" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I4" s="13" t="s">
+      <c r="G14" s="11"/>
+      <c r="H14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="1:9" ht="100" customHeight="1">
+      <c r="A15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="G15" s="11"/>
+      <c r="H15" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="1:9" ht="100" customHeight="1">
+      <c r="A16" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="G16" s="11"/>
+      <c r="H16" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="I16" s="11"/>
+    </row>
+    <row r="17" spans="1:9" ht="100" customHeight="1">
+      <c r="A17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>308</v>
+      </c>
+      <c r="G17" s="11"/>
+      <c r="H17" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="100" customHeight="1">
+      <c r="A18" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="100" customHeight="1">
+      <c r="A19" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="100" customHeight="1">
+      <c r="A20" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="100" customHeight="1">
+      <c r="A21" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="I21" s="11" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="50" customHeight="1">
-      <c r="A5" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I5" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="50" customHeight="1">
-      <c r="A6" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F6" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="50" customHeight="1">
-      <c r="A7" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I7" s="13" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="50" customHeight="1">
-      <c r="A8" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="13" t="s">
+    <row r="22" spans="1:9" ht="100" customHeight="1">
+      <c r="A22" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="170" customHeight="1">
+      <c r="A23" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="170" customHeight="1">
+      <c r="A24" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="G24" s="11"/>
+      <c r="H24" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="50" customHeight="1">
+      <c r="A25" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="50" customHeight="1">
+      <c r="A26" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="11"/>
+      <c r="H26" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="50" customHeight="1">
+      <c r="A27" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G27" s="11"/>
+      <c r="H27" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="I27" s="11" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="180" customHeight="1">
+      <c r="A28" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G28" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>265</v>
+      </c>
+      <c r="I28" s="19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="180" customHeight="1">
+      <c r="A29" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="G29" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I29" s="19" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="180" customHeight="1">
+      <c r="A30" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G30" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="100" customHeight="1">
+      <c r="A31" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>255</v>
+      </c>
+      <c r="I31" s="45" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="100" customHeight="1">
+      <c r="A32" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="I32" s="45" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="100" customHeight="1">
+      <c r="A33" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33" s="20" t="s">
         <v>243</v>
       </c>
-      <c r="F8" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I8" s="13" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="50" customHeight="1">
-      <c r="A9" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>307</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I9" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="100" customHeight="1">
-      <c r="A10" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>306</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="F10" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="50" customHeight="1">
-      <c r="A11" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D11" s="13" t="s">
+      <c r="F33" s="20" t="s">
+        <v>332</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="I33" s="20"/>
+    </row>
+    <row r="34" spans="1:9" ht="100" customHeight="1">
+      <c r="A34" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="50" customHeight="1">
-      <c r="A12" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I12" s="13"/>
-    </row>
-    <row r="13" spans="1:9" ht="100" customHeight="1">
-      <c r="A13" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="I13" s="13"/>
-    </row>
-    <row r="14" spans="1:9" ht="100" customHeight="1">
-      <c r="A14" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="13"/>
-    </row>
-    <row r="15" spans="1:9" ht="100" customHeight="1">
-      <c r="A15" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="16" spans="1:9" ht="100" customHeight="1">
-      <c r="A16" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>231</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="I16" s="13"/>
-    </row>
-    <row r="17" spans="1:9" ht="100" customHeight="1">
-      <c r="A17" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="100" customHeight="1">
-      <c r="A18" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F18" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H18" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="100" customHeight="1">
-      <c r="A19" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H19" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="100" customHeight="1">
-      <c r="A20" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="100" customHeight="1">
-      <c r="A21" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="100" customHeight="1">
-      <c r="A22" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>230</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="170" customHeight="1">
-      <c r="A23" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="170" customHeight="1">
-      <c r="A24" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="G24" s="13"/>
-      <c r="H24" s="17" t="s">
-        <v>264</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="50" customHeight="1">
-      <c r="A25" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F25" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G25" s="13"/>
-      <c r="H25" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="50" customHeight="1">
-      <c r="A26" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>237</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G26" s="13"/>
-      <c r="H26" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="50" customHeight="1">
-      <c r="A27" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="180" customHeight="1">
-      <c r="A28" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G28" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="H28" s="18" t="s">
-        <v>267</v>
-      </c>
-      <c r="I28" s="21" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="180" customHeight="1">
-      <c r="A29" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="H29" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="I29" s="21" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="180" customHeight="1">
-      <c r="A30" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="F30" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="H30" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" ht="100" customHeight="1">
-      <c r="A31" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="H31" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="I31" s="47" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="100" customHeight="1">
-      <c r="A32" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="E32" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="F32" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="H32" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="I32" s="47" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="100" customHeight="1">
-      <c r="A33" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="F33" s="22" t="s">
-        <v>334</v>
-      </c>
-      <c r="G33" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="H33" s="22" t="s">
-        <v>87</v>
-      </c>
-      <c r="I33" s="22"/>
-    </row>
-    <row r="34" spans="1:9" ht="100" customHeight="1">
-      <c r="A34" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E34" s="22" t="s">
+      <c r="E34" s="20" t="s">
         <v>251</v>
       </c>
-      <c r="F34" s="22" t="s">
+      <c r="F34" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G34" s="22" t="s">
+      <c r="G34" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="I34" s="20" t="s">
         <v>335</v>
-      </c>
-      <c r="H34" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="I34" s="22" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="35" spans="1:9" ht="19.5" customHeight="1"/>
     <row r="36" spans="1:9" ht="35" customHeight="1">
-      <c r="A36" s="56" t="s">
-        <v>262</v>
-      </c>
-      <c r="B36" s="57"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="57"/>
-      <c r="E36" s="57"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="57"/>
-      <c r="H36" s="57"/>
-      <c r="I36" s="57"/>
+      <c r="A36" s="54" t="s">
+        <v>260</v>
+      </c>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
     </row>
     <row r="37" spans="1:9" ht="30" customHeight="1">
-      <c r="A37" s="55" t="s">
+      <c r="A37" s="53" t="s">
         <v>90</v>
       </c>
-      <c r="B37" s="55"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
     </row>
     <row r="38" spans="1:9" ht="30" customHeight="1">
-      <c r="A38" s="55" t="s">
+      <c r="A38" s="53" t="s">
         <v>91</v>
       </c>
-      <c r="B38" s="55"/>
-      <c r="C38" s="55"/>
-      <c r="D38" s="55"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
+      <c r="B38" s="53"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="53"/>
+      <c r="I38" s="53"/>
     </row>
     <row r="39" spans="1:9" ht="50" customHeight="1">
-      <c r="A39" s="52" t="s">
-        <v>408</v>
-      </c>
-      <c r="B39" s="52"/>
-      <c r="C39" s="52"/>
-      <c r="D39" s="52"/>
-      <c r="E39" s="52"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="52"/>
-      <c r="H39" s="52"/>
-      <c r="I39" s="52"/>
+      <c r="A39" s="50" t="s">
+        <v>405</v>
+      </c>
+      <c r="B39" s="50"/>
+      <c r="C39" s="50"/>
+      <c r="D39" s="50"/>
+      <c r="E39" s="50"/>
+      <c r="F39" s="50"/>
+      <c r="G39" s="50"/>
+      <c r="H39" s="50"/>
+      <c r="I39" s="50"/>
     </row>
     <row r="40" spans="1:9" ht="30" customHeight="1">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="53" t="s">
         <v>92</v>
       </c>
-      <c r="B40" s="55"/>
-      <c r="C40" s="55"/>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="53"/>
+      <c r="H40" s="53"/>
+      <c r="I40" s="53"/>
     </row>
     <row r="41" spans="1:9" ht="75" customHeight="1">
-      <c r="A41" s="51" t="s">
-        <v>305</v>
-      </c>
-      <c r="B41" s="51"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="51"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
+      <c r="A41" s="49" t="s">
+        <v>303</v>
+      </c>
+      <c r="B41" s="49"/>
+      <c r="C41" s="49"/>
+      <c r="D41" s="49"/>
+      <c r="E41" s="49"/>
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" s="49"/>
-      <c r="B42" s="50"/>
-      <c r="C42" s="50"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="50"/>
-      <c r="I42" s="50"/>
+      <c r="A42" s="47"/>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+      <c r="I42" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -8444,215 +8547,215 @@
     <col min="3" max="3" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" s="42" customFormat="1" ht="35" customHeight="1">
-      <c r="B1" s="70" t="s">
-        <v>299</v>
-      </c>
-      <c r="C1" s="70"/>
+    <row r="1" spans="2:3" s="40" customFormat="1" ht="35" customHeight="1">
+      <c r="B1" s="68" t="s">
+        <v>297</v>
+      </c>
+      <c r="C1" s="68"/>
     </row>
     <row r="2" spans="2:3" ht="50" customHeight="1">
-      <c r="B2" s="71" t="s">
-        <v>318</v>
-      </c>
-      <c r="C2" s="71"/>
+      <c r="B2" s="69" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2" s="69"/>
     </row>
     <row r="4" spans="2:3" ht="15" customHeight="1">
-      <c r="B4" s="44" t="s">
+      <c r="B4" s="42" t="s">
         <v>93</v>
       </c>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="42" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="15" customHeight="1">
-      <c r="B5" s="45" t="s">
+      <c r="B5" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C5" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="6" spans="2:3" ht="15" customHeight="1">
-      <c r="B6" s="45" t="s">
+      <c r="B6" s="43" t="s">
         <v>97</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="15" customHeight="1">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="21" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="15" customHeight="1">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="23" t="s">
+      <c r="C8" s="21" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="15" customHeight="1">
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="43" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="21" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="15" customHeight="1">
-      <c r="B10" s="45" t="s">
+      <c r="B10" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="21" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="15" customHeight="1">
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="21" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="12" spans="2:3" ht="15" customHeight="1">
-      <c r="B12" s="45" t="s">
+      <c r="B12" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="C12" s="23" t="s">
+      <c r="C12" s="21" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="15" customHeight="1">
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="21" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="14" spans="2:3" ht="15" customHeight="1">
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="21" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="15" customHeight="1">
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="23" t="s">
+      <c r="C15" s="21" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="16" spans="2:3" ht="15" customHeight="1">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="23" t="s">
+      <c r="C16" s="21" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="45" t="s">
+      <c r="B17" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="21" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="18" spans="2:3" ht="15" customHeight="1">
-      <c r="B18" s="45" t="s">
+      <c r="B18" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="21" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="19" spans="2:3" ht="15" customHeight="1">
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="21" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="20" spans="2:3" ht="15" customHeight="1">
-      <c r="B20" s="45" t="s">
+      <c r="B20" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="C20" s="23" t="s">
+      <c r="C20" s="21" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="B21" s="45" t="s">
+      <c r="B21" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="21" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="22" spans="2:3" ht="15" customHeight="1">
-      <c r="B22" s="45" t="s">
+      <c r="B22" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="21" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="15" customHeight="1">
-      <c r="B23" s="45" t="s">
+      <c r="B23" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="C23" s="23" t="s">
+      <c r="C23" s="21" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="15" customHeight="1">
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="21" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="15" customHeight="1">
-      <c r="B25" s="45" t="s">
+      <c r="B25" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="C25" s="23" t="s">
+      <c r="C25" s="21" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="15" customHeight="1">
-      <c r="B26" s="45" t="s">
+      <c r="B26" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="21" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="27" spans="2:3" ht="15" customHeight="1">
-      <c r="B27" s="45" t="s">
+      <c r="B27" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="C27" s="23" t="s">
-        <v>319</v>
+      <c r="C27" s="21" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="28" spans="2:3" ht="15" customHeight="1">
-      <c r="B28" s="45" t="s">
+      <c r="B28" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="21" t="s">
         <v>132</v>
       </c>
     </row>
@@ -8682,97 +8785,97 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24" customHeight="1">
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="72" t="s">
+        <v>395</v>
+      </c>
+      <c r="C1" s="72"/>
+    </row>
+    <row r="2" spans="1:4" ht="30" customHeight="1">
+      <c r="B2" s="73" t="s">
+        <v>396</v>
+      </c>
+      <c r="C2" s="73"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+    </row>
+    <row r="4" spans="1:4" ht="19.5" customHeight="1">
+      <c r="B4" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>397</v>
       </c>
-      <c r="C1" s="74"/>
-    </row>
-    <row r="2" spans="1:4" ht="30" customHeight="1">
-      <c r="B2" s="75" t="s">
+    </row>
+    <row r="5" spans="1:4" ht="19.5" customHeight="1">
+      <c r="B5" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="C5" s="44" t="s">
         <v>398</v>
       </c>
-      <c r="C2" s="75"/>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-    </row>
-    <row r="4" spans="1:4" ht="19.5" customHeight="1">
-      <c r="B4" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="19.5" customHeight="1">
-      <c r="B5" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="C5" s="46" t="s">
+      <c r="D5" s="74" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="19.5" customHeight="1">
+      <c r="B6" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="74"/>
+    </row>
+    <row r="7" spans="1:4" ht="19.5" customHeight="1">
+      <c r="B7" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>400</v>
       </c>
-      <c r="D5" s="76" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="19.5" customHeight="1">
-      <c r="B6" s="34" t="s">
-        <v>282</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="D6" s="76"/>
-    </row>
-    <row r="7" spans="1:4" ht="19.5" customHeight="1">
-      <c r="B7" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="23" t="s">
+    </row>
+    <row r="8" spans="1:4" ht="19.5" customHeight="1">
+      <c r="B8" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="19.5" customHeight="1">
-      <c r="B8" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="23" t="s">
+    <row r="9" spans="1:4" ht="19.5" customHeight="1">
+      <c r="B9" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="24" customHeight="1">
+      <c r="B11" s="72" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" s="72"/>
+    </row>
+    <row r="12" spans="1:4" ht="120" customHeight="1">
+      <c r="B12" s="71" t="s">
+        <v>401</v>
+      </c>
+      <c r="C12" s="71"/>
+    </row>
+    <row r="14" spans="1:4" ht="24" customHeight="1">
+      <c r="B14" s="72" t="s">
         <v>404</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" ht="19.5" customHeight="1">
-      <c r="B9" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="24" customHeight="1">
-      <c r="B11" s="74" t="s">
-        <v>280</v>
-      </c>
-      <c r="C11" s="74"/>
-    </row>
-    <row r="12" spans="1:4" ht="120" customHeight="1">
-      <c r="B12" s="73" t="s">
+      <c r="C14" s="72"/>
+    </row>
+    <row r="15" spans="1:4" ht="120" customHeight="1">
+      <c r="A15" s="46"/>
+      <c r="B15" s="70" t="s">
         <v>403</v>
       </c>
-      <c r="C12" s="73"/>
-    </row>
-    <row r="14" spans="1:4" ht="24" customHeight="1">
-      <c r="B14" s="74" t="s">
-        <v>406</v>
-      </c>
-      <c r="C14" s="74"/>
-    </row>
-    <row r="15" spans="1:4" ht="120" customHeight="1">
-      <c r="A15" s="48"/>
-      <c r="B15" s="72" t="s">
-        <v>405</v>
-      </c>
-      <c r="C15" s="73"/>
+      <c r="C15" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -8805,196 +8908,196 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="24" customHeight="1">
-      <c r="B1" s="74" t="s">
-        <v>302</v>
-      </c>
-      <c r="C1" s="74"/>
+      <c r="B1" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" s="72"/>
     </row>
     <row r="2" spans="2:4" ht="30" customHeight="1">
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="73" t="s">
+        <v>406</v>
+      </c>
+      <c r="C2" s="73"/>
+    </row>
+    <row r="3" spans="2:4">
+      <c r="B3" s="31"/>
+      <c r="C3" s="31"/>
+    </row>
+    <row r="4" spans="2:4" ht="19.5" customHeight="1">
+      <c r="B4" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="19.5" customHeight="1">
+      <c r="B5" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>399</v>
+      </c>
+      <c r="D5" s="74" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="19.5" customHeight="1">
+      <c r="B6" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D6" s="74"/>
+    </row>
+    <row r="7" spans="2:4" ht="19.5" customHeight="1">
+      <c r="B7" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="19.5" customHeight="1">
+      <c r="B8" s="32" t="s">
+        <v>170</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" ht="19.5" customHeight="1">
+      <c r="B9" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" ht="24" customHeight="1">
+      <c r="B11" s="72" t="s">
+        <v>278</v>
+      </c>
+      <c r="C11" s="72"/>
+    </row>
+    <row r="12" spans="2:4" ht="300" customHeight="1">
+      <c r="B12" s="71" t="s">
+        <v>337</v>
+      </c>
+      <c r="C12" s="71"/>
+    </row>
+    <row r="14" spans="2:4" ht="24" customHeight="1">
+      <c r="B14" s="72" t="s">
+        <v>407</v>
+      </c>
+      <c r="C14" s="72"/>
+    </row>
+    <row r="15" spans="2:4" ht="15" customHeight="1">
+      <c r="B15" s="33" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" ht="15" customHeight="1">
+      <c r="B16" s="35" t="s">
+        <v>176</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="15" customHeight="1">
+      <c r="B17" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="15" customHeight="1">
+      <c r="B18" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="15" customHeight="1">
+      <c r="B19" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" ht="15" customHeight="1">
+      <c r="B20" s="35" t="s">
+        <v>184</v>
+      </c>
+      <c r="C20" s="36" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" ht="15" customHeight="1">
+      <c r="B21" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" ht="15" customHeight="1">
+      <c r="B22" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="C22" s="36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" ht="15" customHeight="1">
+      <c r="B23" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" ht="15" customHeight="1">
+      <c r="B24" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" ht="15" customHeight="1">
+      <c r="B25" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" ht="24" customHeight="1">
+      <c r="B27" s="72" t="s">
+        <v>408</v>
+      </c>
+      <c r="C27" s="72"/>
+    </row>
+    <row r="28" spans="2:3">
+      <c r="B28" s="77">
+        <v>46204</v>
+      </c>
+      <c r="C28" s="78"/>
+    </row>
+    <row r="29" spans="2:3" ht="300" customHeight="1">
+      <c r="B29" s="75" t="s">
         <v>409</v>
       </c>
-      <c r="C2" s="75"/>
-    </row>
-    <row r="3" spans="2:4">
-      <c r="B3" s="33"/>
-      <c r="C3" s="33"/>
-    </row>
-    <row r="4" spans="2:4" ht="19.5" customHeight="1">
-      <c r="B4" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="19.5" customHeight="1">
-      <c r="B5" s="34" t="s">
-        <v>281</v>
-      </c>
-      <c r="C5" s="46" t="s">
-        <v>401</v>
-      </c>
-      <c r="D5" s="76" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="19.5" customHeight="1">
-      <c r="B6" s="34" t="s">
-        <v>282</v>
-      </c>
-      <c r="C6" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="D6" s="76"/>
-    </row>
-    <row r="7" spans="2:4" ht="19.5" customHeight="1">
-      <c r="B7" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="19.5" customHeight="1">
-      <c r="B8" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="19.5" customHeight="1">
-      <c r="B9" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" ht="24" customHeight="1">
-      <c r="B11" s="74" t="s">
-        <v>280</v>
-      </c>
-      <c r="C11" s="74"/>
-    </row>
-    <row r="12" spans="2:4" ht="300" customHeight="1">
-      <c r="B12" s="73" t="s">
-        <v>339</v>
-      </c>
-      <c r="C12" s="73"/>
-    </row>
-    <row r="14" spans="2:4" ht="24" customHeight="1">
-      <c r="B14" s="74" t="s">
-        <v>410</v>
-      </c>
-      <c r="C14" s="74"/>
-    </row>
-    <row r="15" spans="2:4" ht="15" customHeight="1">
-      <c r="B15" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="2:4" ht="15" customHeight="1">
-      <c r="B16" s="37" t="s">
-        <v>176</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" ht="15" customHeight="1">
-      <c r="B17" s="35" t="s">
-        <v>178</v>
-      </c>
-      <c r="C17" s="36" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" ht="15" customHeight="1">
-      <c r="B18" s="37" t="s">
-        <v>180</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" ht="15" customHeight="1">
-      <c r="B19" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="C19" s="36" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" ht="15" customHeight="1">
-      <c r="B20" s="37" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="38" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" ht="15" customHeight="1">
-      <c r="B21" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="C21" s="36" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="22" spans="2:3" ht="15" customHeight="1">
-      <c r="B22" s="37" t="s">
-        <v>188</v>
-      </c>
-      <c r="C22" s="38" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" ht="15" customHeight="1">
-      <c r="B23" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" ht="15" customHeight="1">
-      <c r="B24" s="37" t="s">
-        <v>192</v>
-      </c>
-      <c r="C24" s="38" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="25" spans="2:3" ht="15" customHeight="1">
-      <c r="B25" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="C25" s="36" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" ht="24" customHeight="1">
-      <c r="B27" s="74" t="s">
-        <v>411</v>
-      </c>
-      <c r="C27" s="74"/>
-    </row>
-    <row r="28" spans="2:3">
-      <c r="B28" s="79">
-        <v>46204</v>
-      </c>
-      <c r="C28" s="80"/>
-    </row>
-    <row r="29" spans="2:3" ht="300" customHeight="1">
-      <c r="B29" s="77" t="s">
-        <v>412</v>
-      </c>
-      <c r="C29" s="78"/>
+      <c r="C29" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -9028,99 +9131,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="35" customHeight="1">
-      <c r="B1" s="81" t="s">
+      <c r="B1" s="79" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
     </row>
     <row r="2" spans="2:4" ht="42" customHeight="1">
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="80" t="s">
+        <v>307</v>
+      </c>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+    </row>
+    <row r="3" spans="2:4" ht="21.5" customHeight="1">
+      <c r="B3" s="81" t="s">
+        <v>197</v>
+      </c>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+    </row>
+    <row r="4" spans="2:4" ht="35" customHeight="1">
+      <c r="B4" s="41" t="s">
+        <v>198</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>199</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" ht="55.5" customHeight="1">
+      <c r="B5" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" ht="55.5" customHeight="1">
+      <c r="B6" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>309</v>
       </c>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-    </row>
-    <row r="3" spans="2:4" ht="21.5" customHeight="1">
-      <c r="B3" s="83" t="s">
-        <v>197</v>
-      </c>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-    </row>
-    <row r="4" spans="2:4" ht="35" customHeight="1">
-      <c r="B4" s="43" t="s">
-        <v>198</v>
-      </c>
-      <c r="C4" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="D4" s="43" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="55.5" customHeight="1">
-      <c r="B5" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="C5" s="25" t="s">
+      <c r="D6" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" ht="55.5" customHeight="1">
+      <c r="B7" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" ht="55.5" customHeight="1">
+      <c r="B8" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>314</v>
       </c>
-      <c r="D5" s="25" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="55.5" customHeight="1">
-      <c r="B6" s="26" t="s">
-        <v>202</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>311</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="55.5" customHeight="1">
-      <c r="B7" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>312</v>
-      </c>
-      <c r="D7" s="25" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="55.5" customHeight="1">
-      <c r="B8" s="26" t="s">
-        <v>205</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>313</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>316</v>
-      </c>
     </row>
     <row r="9" spans="2:4">
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
     </row>
     <row r="10" spans="2:4" ht="42" customHeight="1">
-      <c r="B10" s="82" t="s">
-        <v>268</v>
-      </c>
-      <c r="C10" s="82"/>
-      <c r="D10" s="82"/>
+      <c r="B10" s="80" t="s">
+        <v>266</v>
+      </c>
+      <c r="C10" s="80"/>
+      <c r="D10" s="80"/>
     </row>
     <row r="12" spans="2:4" ht="100" customHeight="1">
-      <c r="B12" s="84" t="s">
-        <v>413</v>
-      </c>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
+      <c r="B12" s="82" t="s">
+        <v>410</v>
+      </c>
+      <c r="C12" s="83"/>
+      <c r="D12" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9153,587 +9256,587 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="35" customHeight="1">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>206</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+      <c r="F1" s="85"/>
+      <c r="G1" s="85"/>
     </row>
     <row r="2" spans="1:7" ht="42" customHeight="1">
-      <c r="A2" s="88" t="s">
-        <v>303</v>
-      </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
+      <c r="A2" s="86" t="s">
+        <v>301</v>
+      </c>
+      <c r="B2" s="86"/>
+      <c r="C2" s="86"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
     </row>
     <row r="3" spans="1:7" ht="30" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="D3" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="C3" s="28" t="s">
+      <c r="E3" s="26" t="s">
         <v>271</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="F3" s="26" t="s">
+        <v>207</v>
+      </c>
+      <c r="G3" s="26" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A4" s="27" t="s">
+        <v>174</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F4" s="28"/>
+      <c r="G4" s="27"/>
+    </row>
+    <row r="5" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A5" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="29"/>
+    </row>
+    <row r="6" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A6" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F6" s="28"/>
+      <c r="G6" s="27"/>
+    </row>
+    <row r="7" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A7" s="29" t="s">
+        <v>180</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="29"/>
+      <c r="E7" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" s="30"/>
+      <c r="G7" s="29"/>
+    </row>
+    <row r="8" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A8" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="B8" s="28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" s="28"/>
+      <c r="G8" s="27"/>
+    </row>
+    <row r="9" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A9" s="29" t="s">
+        <v>184</v>
+      </c>
+      <c r="B9" s="30" t="s">
         <v>272</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="C9" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F9" s="30"/>
+      <c r="G9" s="29"/>
+    </row>
+    <row r="10" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A10" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="B10" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F10" s="28"/>
+      <c r="G10" s="27"/>
+    </row>
+    <row r="11" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A11" s="29" t="s">
+        <v>188</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F11" s="30"/>
+      <c r="G11" s="29"/>
+    </row>
+    <row r="12" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A12" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="B12" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="F3" s="28" t="s">
-        <v>207</v>
-      </c>
-      <c r="G3" s="28" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A4" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="B4" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="29"/>
-      <c r="E4" s="29" t="s">
+      <c r="C12" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="F4" s="30"/>
-      <c r="G4" s="29"/>
-    </row>
-    <row r="5" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A5" s="31" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31" t="s">
+      <c r="F12" s="28"/>
+      <c r="G12" s="27"/>
+    </row>
+    <row r="13" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A13" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="F5" s="32"/>
-      <c r="G5" s="31"/>
-    </row>
-    <row r="6" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A6" s="29" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29" t="s">
+      <c r="F13" s="30"/>
+      <c r="G13" s="29"/>
+    </row>
+    <row r="14" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A14" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="29"/>
-    </row>
-    <row r="7" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>180</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="31"/>
-      <c r="E7" s="31" t="s">
+      <c r="F14" s="28"/>
+      <c r="G14" s="27"/>
+    </row>
+    <row r="15" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A15" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="F7" s="32"/>
-      <c r="G7" s="31"/>
-    </row>
-    <row r="8" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A8" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="B8" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29" t="s">
+      <c r="F15" s="30"/>
+      <c r="G15" s="29"/>
+    </row>
+    <row r="16" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A16" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="29"/>
-    </row>
-    <row r="9" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A9" s="31" t="s">
-        <v>184</v>
-      </c>
-      <c r="B9" s="32" t="s">
+      <c r="F16" s="28"/>
+      <c r="G16" s="27"/>
+    </row>
+    <row r="17" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A17" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D17" s="29"/>
+      <c r="E17" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F17" s="30"/>
+      <c r="G17" s="29"/>
+    </row>
+    <row r="18" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A18" s="27" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F18" s="28"/>
+      <c r="G18" s="27"/>
+    </row>
+    <row r="19" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A19" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F19" s="30"/>
+      <c r="G19" s="29"/>
+    </row>
+    <row r="20" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A20" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="27"/>
+    </row>
+    <row r="21" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A21" s="29" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" s="30" t="s">
         <v>274</v>
       </c>
-      <c r="C9" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31" t="s">
+      <c r="C21" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="F9" s="32"/>
-      <c r="G9" s="31"/>
-    </row>
-    <row r="10" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A10" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="B10" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29" t="s">
+      <c r="F21" s="30"/>
+      <c r="G21" s="29"/>
+    </row>
+    <row r="22" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A22" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B22" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D22" s="27"/>
+      <c r="E22" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="29"/>
-    </row>
-    <row r="11" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A11" s="31" t="s">
-        <v>188</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="31"/>
-      <c r="E11" s="31" t="s">
+      <c r="F22" s="28"/>
+      <c r="G22" s="27"/>
+    </row>
+    <row r="23" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A23" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="B23" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="F11" s="32"/>
-      <c r="G11" s="31"/>
-    </row>
-    <row r="12" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A12" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="B12" s="30" t="s">
+      <c r="F23" s="30"/>
+      <c r="G23" s="29"/>
+    </row>
+    <row r="24" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A24" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="27"/>
+      <c r="E24" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F24" s="28"/>
+      <c r="G24" s="27"/>
+    </row>
+    <row r="25" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A25" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="B25" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F25" s="30"/>
+      <c r="G25" s="29"/>
+    </row>
+    <row r="26" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A26" s="27" t="s">
+        <v>221</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="27"/>
+      <c r="E26" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F26" s="28"/>
+      <c r="G26" s="27"/>
+    </row>
+    <row r="27" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A27" s="29" t="s">
+        <v>222</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F27" s="30"/>
+      <c r="G27" s="29"/>
+    </row>
+    <row r="28" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A28" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="C28" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D28" s="27"/>
+      <c r="E28" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F28" s="28"/>
+      <c r="G28" s="27"/>
+    </row>
+    <row r="29" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A29" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="B29" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F29" s="30"/>
+      <c r="G29" s="29"/>
+    </row>
+    <row r="30" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A30" s="27" t="s">
+        <v>225</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C30" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27" t="s">
+        <v>209</v>
+      </c>
+      <c r="F30" s="28"/>
+      <c r="G30" s="27"/>
+    </row>
+    <row r="31" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A31" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="B31" s="30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C31" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="C12" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29" t="s">
+      <c r="D31" s="29"/>
+      <c r="E31" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="F12" s="30"/>
-      <c r="G12" s="29"/>
-    </row>
-    <row r="13" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A13" s="31" t="s">
-        <v>192</v>
-      </c>
-      <c r="B13" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31" t="s">
+      <c r="F31" s="30"/>
+      <c r="G31" s="29"/>
+    </row>
+    <row r="32" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A32" s="27" t="s">
+        <v>227</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="F13" s="32"/>
-      <c r="G13" s="31"/>
-    </row>
-    <row r="14" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A14" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="B14" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29" t="s">
+      <c r="F32" s="28"/>
+      <c r="G32" s="27"/>
+    </row>
+    <row r="33" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A33" s="29" t="s">
+        <v>228</v>
+      </c>
+      <c r="B33" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="D33" s="29"/>
+      <c r="E33" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="29"/>
-    </row>
-    <row r="15" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A15" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="B15" s="32" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31" t="s">
+      <c r="F33" s="30"/>
+      <c r="G33" s="29"/>
+    </row>
+    <row r="34" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A34" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="D34" s="27"/>
+      <c r="E34" s="27" t="s">
         <v>209</v>
       </c>
-      <c r="F15" s="32"/>
-      <c r="G15" s="31"/>
-    </row>
-    <row r="16" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A16" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="B16" s="30" t="s">
-        <v>37</v>
-      </c>
-      <c r="C16" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="29"/>
-      <c r="E16" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="29"/>
-    </row>
-    <row r="17" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A17" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="F17" s="32"/>
-      <c r="G17" s="31"/>
-    </row>
-    <row r="18" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A18" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="B18" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="29"/>
-      <c r="E18" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F18" s="30"/>
-      <c r="G18" s="29"/>
-    </row>
-    <row r="19" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A19" s="31" t="s">
-        <v>214</v>
-      </c>
-      <c r="B19" s="32" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="31"/>
-      <c r="E19" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="31"/>
-    </row>
-    <row r="20" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="30" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="30" t="s">
-        <v>42</v>
-      </c>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="29"/>
-    </row>
-    <row r="21" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A21" s="31" t="s">
-        <v>216</v>
-      </c>
-      <c r="B21" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="F21" s="32"/>
-      <c r="G21" s="31"/>
-    </row>
-    <row r="22" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A22" s="29" t="s">
-        <v>217</v>
-      </c>
-      <c r="B22" s="30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="29"/>
-      <c r="E22" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F22" s="30"/>
-      <c r="G22" s="29"/>
-    </row>
-    <row r="23" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A23" s="31" t="s">
-        <v>218</v>
-      </c>
-      <c r="B23" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="D23" s="31"/>
-      <c r="E23" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="F23" s="32"/>
-      <c r="G23" s="31"/>
-    </row>
-    <row r="24" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="B24" s="30" t="s">
-        <v>59</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F24" s="30"/>
-      <c r="G24" s="29"/>
-    </row>
-    <row r="25" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A25" s="31" t="s">
-        <v>220</v>
-      </c>
-      <c r="B25" s="32" t="s">
-        <v>62</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="F25" s="32"/>
-      <c r="G25" s="31"/>
-    </row>
-    <row r="26" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>221</v>
-      </c>
-      <c r="B26" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F26" s="30"/>
-      <c r="G26" s="29"/>
-    </row>
-    <row r="27" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A27" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="B27" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="31"/>
-      <c r="E27" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="F27" s="32"/>
-      <c r="G27" s="31"/>
-    </row>
-    <row r="28" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A28" s="29" t="s">
-        <v>223</v>
-      </c>
-      <c r="B28" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F28" s="30"/>
-      <c r="G28" s="29"/>
-    </row>
-    <row r="29" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A29" s="31" t="s">
-        <v>224</v>
-      </c>
-      <c r="B29" s="32" t="s">
-        <v>74</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="F29" s="32"/>
-      <c r="G29" s="31"/>
-    </row>
-    <row r="30" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>225</v>
-      </c>
-      <c r="B30" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="C30" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F30" s="30"/>
-      <c r="G30" s="29"/>
-    </row>
-    <row r="31" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A31" s="31" t="s">
-        <v>226</v>
-      </c>
-      <c r="B31" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="C31" s="32" t="s">
+      <c r="F34" s="28"/>
+      <c r="G34" s="27"/>
+    </row>
+    <row r="36" spans="1:7" ht="43.5" customHeight="1">
+      <c r="A36" s="84" t="s">
         <v>277</v>
       </c>
-      <c r="D31" s="31"/>
-      <c r="E31" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="F31" s="32"/>
-      <c r="G31" s="31"/>
-    </row>
-    <row r="32" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="B32" s="30" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F32" s="30"/>
-      <c r="G32" s="29"/>
-    </row>
-    <row r="33" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A33" s="31" t="s">
-        <v>228</v>
-      </c>
-      <c r="B33" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="F33" s="32"/>
-      <c r="G33" s="31"/>
-    </row>
-    <row r="34" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>229</v>
-      </c>
-      <c r="B34" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="D34" s="29"/>
-      <c r="E34" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="F34" s="30"/>
-      <c r="G34" s="29"/>
-    </row>
-    <row r="36" spans="1:7" ht="43.5" customHeight="1">
-      <c r="A36" s="86" t="s">
-        <v>279</v>
-      </c>
-      <c r="B36" s="86"/>
-      <c r="C36" s="86"/>
-      <c r="D36" s="86"/>
-      <c r="E36" s="86"/>
-      <c r="F36" s="86"/>
-      <c r="G36" s="86"/>
+      <c r="B36" s="84"/>
+      <c r="C36" s="84"/>
+      <c r="D36" s="84"/>
+      <c r="E36" s="84"/>
+      <c r="F36" s="84"/>
+      <c r="G36" s="84"/>
     </row>
   </sheetData>
   <mergeCells count="3">
